--- a/research/traditional_assets/database/data/belgium/belgium_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_beverage_soft.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07946791842877482</v>
+        <v>0.07930299863270288</v>
       </c>
       <c r="C2">
-        <v>756.5632089915974</v>
+        <v>750.767738876444</v>
       </c>
       <c r="D2">
-        <v>633.2632089915975</v>
+        <v>635.0379388764441</v>
       </c>
       <c r="E2">
-        <v>-5.02</v>
+        <v>2.5502</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.5702</v>
       </c>
       <c r="G2">
         <v>123.3</v>
@@ -1451,28 +1451,28 @@
         <v>41.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3807810599999999</v>
       </c>
       <c r="N2">
-        <v>41.4</v>
+        <v>41.01921894</v>
       </c>
       <c r="O2">
-        <v>10.35</v>
+        <v>10.254804735</v>
       </c>
       <c r="P2">
-        <v>31.05</v>
+        <v>30.764414205</v>
       </c>
       <c r="Q2">
-        <v>54.45</v>
+        <v>54.164414205</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07946791842877482</v>
+        <v>0.07972297841687159</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6612219901513506</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>108.7238950382669</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07930299863270288</v>
+        <v>0.07913807883663096</v>
       </c>
       <c r="C3">
-        <v>750.767738876444</v>
+        <v>744.9822441330297</v>
       </c>
       <c r="D3">
-        <v>635.0379388764441</v>
+        <v>636.8226441330297</v>
       </c>
       <c r="E3">
-        <v>2.5502</v>
+        <v>10.1204</v>
       </c>
       <c r="F3">
-        <v>7.5702</v>
+        <v>15.1404</v>
       </c>
       <c r="G3">
         <v>123.3</v>
@@ -1533,28 +1533,28 @@
         <v>41.4</v>
       </c>
       <c r="M3">
-        <v>0.3807810599999999</v>
+        <v>0.7615621199999999</v>
       </c>
       <c r="N3">
-        <v>41.01921894</v>
+        <v>40.63843788</v>
       </c>
       <c r="O3">
-        <v>10.254804735</v>
+        <v>10.15960947</v>
       </c>
       <c r="P3">
-        <v>30.764414205</v>
+        <v>30.47882841</v>
       </c>
       <c r="Q3">
-        <v>54.164414205</v>
+        <v>53.87882841</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07972297841687159</v>
+        <v>0.07998324371084792</v>
       </c>
       <c r="T3">
-        <v>0.6612219901513506</v>
+        <v>0.6662950451624858</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>108.7238950382669</v>
+        <v>54.36194751913344</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07913807883663096</v>
+        <v>0.07897315904055902</v>
       </c>
       <c r="C4">
-        <v>744.9822441330297</v>
+        <v>739.2068091024881</v>
       </c>
       <c r="D4">
-        <v>636.8226441330297</v>
+        <v>638.6174091024882</v>
       </c>
       <c r="E4">
-        <v>10.1204</v>
+        <v>17.6906</v>
       </c>
       <c r="F4">
-        <v>15.1404</v>
+        <v>22.7106</v>
       </c>
       <c r="G4">
         <v>123.3</v>
@@ -1615,28 +1615,28 @@
         <v>41.4</v>
       </c>
       <c r="M4">
-        <v>0.7615621199999999</v>
+        <v>1.14234318</v>
       </c>
       <c r="N4">
-        <v>40.63843788</v>
+        <v>40.25765682</v>
       </c>
       <c r="O4">
-        <v>10.15960947</v>
+        <v>10.064414205</v>
       </c>
       <c r="P4">
-        <v>30.47882841</v>
+        <v>30.193242615</v>
       </c>
       <c r="Q4">
-        <v>53.87882841</v>
+        <v>53.593242615</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07998324371084792</v>
+        <v>0.08024887529954537</v>
       </c>
       <c r="T4">
-        <v>0.6662950451624858</v>
+        <v>0.6714726992460154</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>54.36194751913344</v>
+        <v>36.24129834608896</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07897315904055902</v>
+        <v>0.07880823924448707</v>
       </c>
       <c r="C5">
-        <v>739.2068091024881</v>
+        <v>733.4415190794376</v>
       </c>
       <c r="D5">
-        <v>638.6174091024882</v>
+        <v>640.4223190794377</v>
       </c>
       <c r="E5">
-        <v>17.6906</v>
+        <v>25.2608</v>
       </c>
       <c r="F5">
-        <v>22.7106</v>
+        <v>30.2808</v>
       </c>
       <c r="G5">
         <v>123.3</v>
@@ -1697,28 +1697,28 @@
         <v>41.4</v>
       </c>
       <c r="M5">
-        <v>1.14234318</v>
+        <v>1.52312424</v>
       </c>
       <c r="N5">
-        <v>40.25765682</v>
+        <v>39.87687576</v>
       </c>
       <c r="O5">
-        <v>10.064414205</v>
+        <v>9.969218939999999</v>
       </c>
       <c r="P5">
-        <v>30.193242615</v>
+        <v>29.90765682</v>
       </c>
       <c r="Q5">
-        <v>53.593242615</v>
+        <v>53.30765682</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08024887529954537</v>
+        <v>0.08052004087967404</v>
       </c>
       <c r="T5">
-        <v>0.6714726992460154</v>
+        <v>0.6767582211229519</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.24129834608896</v>
+        <v>27.18097375956672</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07880823924448707</v>
+        <v>0.07864331944841514</v>
       </c>
       <c r="C6">
-        <v>733.4415190794376</v>
+        <v>727.686460325495</v>
       </c>
       <c r="D6">
-        <v>640.4223190794377</v>
+        <v>642.237460325495</v>
       </c>
       <c r="E6">
-        <v>25.2608</v>
+        <v>32.831</v>
       </c>
       <c r="F6">
-        <v>30.2808</v>
+        <v>37.851</v>
       </c>
       <c r="G6">
         <v>123.3</v>
@@ -1779,28 +1779,28 @@
         <v>41.4</v>
       </c>
       <c r="M6">
-        <v>1.52312424</v>
+        <v>1.9039053</v>
       </c>
       <c r="N6">
-        <v>39.87687576</v>
+        <v>39.4960947</v>
       </c>
       <c r="O6">
-        <v>9.969218939999999</v>
+        <v>9.874023675</v>
       </c>
       <c r="P6">
-        <v>29.90765682</v>
+        <v>29.622071025</v>
       </c>
       <c r="Q6">
-        <v>53.30765682</v>
+        <v>53.022071025</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08052004087967404</v>
+        <v>0.08079691520885804</v>
       </c>
       <c r="T6">
-        <v>0.6767582211229519</v>
+        <v>0.6821550171446661</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.18097375956672</v>
+        <v>21.74477900765337</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07864331944841514</v>
+        <v>0.0784783996523432</v>
       </c>
       <c r="C7">
-        <v>727.686460325495</v>
+        <v>721.9417200830177</v>
       </c>
       <c r="D7">
-        <v>642.237460325495</v>
+        <v>644.0629200830177</v>
       </c>
       <c r="E7">
-        <v>32.831</v>
+        <v>40.4012</v>
       </c>
       <c r="F7">
-        <v>37.851</v>
+        <v>45.42120000000001</v>
       </c>
       <c r="G7">
         <v>123.3</v>
@@ -1861,28 +1861,28 @@
         <v>41.4</v>
       </c>
       <c r="M7">
-        <v>1.9039053</v>
+        <v>2.28468636</v>
       </c>
       <c r="N7">
-        <v>39.4960947</v>
+        <v>39.11531364</v>
       </c>
       <c r="O7">
-        <v>9.874023675</v>
+        <v>9.778828409999999</v>
       </c>
       <c r="P7">
-        <v>29.622071025</v>
+        <v>29.33648523</v>
       </c>
       <c r="Q7">
-        <v>53.022071025</v>
+        <v>52.73648523</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08079691520885804</v>
+        <v>0.08107968048121617</v>
       </c>
       <c r="T7">
-        <v>0.6821550171446661</v>
+        <v>0.6876666386136507</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.74477900765337</v>
+        <v>18.12064917304448</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0784783996523432</v>
+        <v>0.07831347985627127</v>
       </c>
       <c r="C8">
-        <v>721.9417200830177</v>
+        <v>716.2073865890815</v>
       </c>
       <c r="D8">
-        <v>644.0629200830177</v>
+        <v>645.8987865890815</v>
       </c>
       <c r="E8">
-        <v>40.4012</v>
+        <v>47.97139999999999</v>
       </c>
       <c r="F8">
-        <v>45.4212</v>
+        <v>52.99139999999999</v>
       </c>
       <c r="G8">
         <v>123.3</v>
@@ -1943,28 +1943,28 @@
         <v>41.4</v>
       </c>
       <c r="M8">
-        <v>2.28468636</v>
+        <v>2.665467419999999</v>
       </c>
       <c r="N8">
-        <v>39.11531364</v>
+        <v>38.73453258</v>
       </c>
       <c r="O8">
-        <v>9.778828409999999</v>
+        <v>9.683633145</v>
       </c>
       <c r="P8">
-        <v>29.33648523</v>
+        <v>29.050899435</v>
       </c>
       <c r="Q8">
-        <v>52.73648523</v>
+        <v>52.450899435</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08107968048121617</v>
+        <v>0.0813685267271734</v>
       </c>
       <c r="T8">
-        <v>0.6876666386136507</v>
+        <v>0.693296789576592</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.12064917304448</v>
+        <v>15.5319850054667</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07831347985627125</v>
+        <v>0.07814856006019932</v>
       </c>
       <c r="C9">
-        <v>716.2073865890816</v>
+        <v>710.4835490896984</v>
       </c>
       <c r="D9">
-        <v>645.8987865890816</v>
+        <v>647.7451490896984</v>
       </c>
       <c r="E9">
-        <v>47.9714</v>
+        <v>55.5416</v>
       </c>
       <c r="F9">
-        <v>52.99140000000001</v>
+        <v>60.5616</v>
       </c>
       <c r="G9">
         <v>123.3</v>
@@ -2025,28 +2025,28 @@
         <v>41.4</v>
       </c>
       <c r="M9">
-        <v>2.66546742</v>
+        <v>3.04624848</v>
       </c>
       <c r="N9">
-        <v>38.73453258</v>
+        <v>38.35375152</v>
       </c>
       <c r="O9">
-        <v>9.683633145</v>
+        <v>9.588437879999999</v>
       </c>
       <c r="P9">
-        <v>29.050899435</v>
+        <v>28.76531364</v>
       </c>
       <c r="Q9">
-        <v>52.450899435</v>
+        <v>52.16531363999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0813685267271734</v>
+        <v>0.0816636522393471</v>
       </c>
       <c r="T9">
-        <v>0.693296789576592</v>
+        <v>0.6990493351256842</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.53198500546669</v>
+        <v>13.59048687978336</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07814856006019932</v>
+        <v>0.07808489026412739</v>
       </c>
       <c r="C10">
-        <v>710.4835490896984</v>
+        <v>703.6289928601166</v>
       </c>
       <c r="D10">
-        <v>647.7451490896984</v>
+        <v>648.4607928601166</v>
       </c>
       <c r="E10">
-        <v>55.5416</v>
+        <v>63.1118</v>
       </c>
       <c r="F10">
-        <v>60.5616</v>
+        <v>68.1318</v>
       </c>
       <c r="G10">
         <v>123.3</v>
@@ -2107,45 +2107,45 @@
         <v>41.4</v>
       </c>
       <c r="M10">
-        <v>3.04624848</v>
+        <v>3.52922724</v>
       </c>
       <c r="N10">
-        <v>38.35375152</v>
+        <v>37.87077276</v>
       </c>
       <c r="O10">
-        <v>9.588437879999999</v>
+        <v>9.46769319</v>
       </c>
       <c r="P10">
-        <v>28.76531364</v>
+        <v>28.40307957</v>
       </c>
       <c r="Q10">
-        <v>52.16531363999999</v>
+        <v>51.80307957</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0816636522393471</v>
+        <v>0.08196526402651361</v>
       </c>
       <c r="T10">
-        <v>0.6990493351256842</v>
+        <v>0.7049283102472839</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.59048687978336</v>
+        <v>11.73061329992455</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07808489026412739</v>
+        <v>0.07793122046805544</v>
       </c>
       <c r="C11">
-        <v>703.6289928601166</v>
+        <v>697.7925613850102</v>
       </c>
       <c r="D11">
-        <v>648.4607928601166</v>
+        <v>650.1945613850103</v>
       </c>
       <c r="E11">
-        <v>63.1118</v>
+        <v>70.682</v>
       </c>
       <c r="F11">
-        <v>68.1318</v>
+        <v>75.702</v>
       </c>
       <c r="G11">
         <v>123.3</v>
@@ -2189,28 +2189,28 @@
         <v>41.4</v>
       </c>
       <c r="M11">
-        <v>3.52922724</v>
+        <v>3.9213636</v>
       </c>
       <c r="N11">
-        <v>37.87077276</v>
+        <v>37.4786364</v>
       </c>
       <c r="O11">
-        <v>9.46769319</v>
+        <v>9.3696591</v>
       </c>
       <c r="P11">
-        <v>28.40307957</v>
+        <v>28.1089773</v>
       </c>
       <c r="Q11">
-        <v>51.80307957</v>
+        <v>51.5089773</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08196526402651361</v>
+        <v>0.08227357829783938</v>
       </c>
       <c r="T11">
-        <v>0.7049283102472839</v>
+        <v>0.7109379292604747</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.73061329992455</v>
+        <v>10.55755196993209</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07793122046805544</v>
+        <v>0.07791780067198351</v>
       </c>
       <c r="C12">
-        <v>697.7925613850102</v>
+        <v>690.3742095471038</v>
       </c>
       <c r="D12">
-        <v>650.1945613850103</v>
+        <v>650.3464095471038</v>
       </c>
       <c r="E12">
-        <v>70.682</v>
+        <v>78.2522</v>
       </c>
       <c r="F12">
-        <v>75.702</v>
+        <v>83.2722</v>
       </c>
       <c r="G12">
         <v>123.3</v>
@@ -2271,45 +2271,45 @@
         <v>41.4</v>
       </c>
       <c r="M12">
-        <v>3.9213636</v>
+        <v>4.4550627</v>
       </c>
       <c r="N12">
-        <v>37.4786364</v>
+        <v>36.9449373</v>
       </c>
       <c r="O12">
-        <v>9.3696591</v>
+        <v>9.236234325</v>
       </c>
       <c r="P12">
-        <v>28.1089773</v>
+        <v>27.708702975</v>
       </c>
       <c r="Q12">
-        <v>51.5089773</v>
+        <v>51.108702975</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08227357829783938</v>
+        <v>0.08258882097975676</v>
       </c>
       <c r="T12">
-        <v>0.7109379292604747</v>
+        <v>0.7170825958919396</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.55755196993209</v>
+        <v>9.292798505394773</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07791780067198351</v>
+        <v>0.07777688087591157</v>
       </c>
       <c r="C13">
-        <v>690.3742095471038</v>
+        <v>684.4028437057481</v>
       </c>
       <c r="D13">
-        <v>650.3464095471038</v>
+        <v>651.9452437057481</v>
       </c>
       <c r="E13">
-        <v>78.2522</v>
+        <v>85.8224</v>
       </c>
       <c r="F13">
-        <v>83.2722</v>
+        <v>90.8424</v>
       </c>
       <c r="G13">
         <v>123.3</v>
@@ -2353,28 +2353,28 @@
         <v>41.4</v>
       </c>
       <c r="M13">
-        <v>4.4550627</v>
+        <v>4.860068399999999</v>
       </c>
       <c r="N13">
-        <v>36.9449373</v>
+        <v>36.5399316</v>
       </c>
       <c r="O13">
-        <v>9.236234325</v>
+        <v>9.134982900000001</v>
       </c>
       <c r="P13">
-        <v>27.708702975</v>
+        <v>27.4049487</v>
       </c>
       <c r="Q13">
-        <v>51.108702975</v>
+        <v>50.8049487</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08258882097975676</v>
+        <v>0.08291122826808134</v>
       </c>
       <c r="T13">
-        <v>0.7170825958919396</v>
+        <v>0.7233669140377558</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.292798505394773</v>
+        <v>8.51839862994521</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07777688087591157</v>
+        <v>0.07763596107983964</v>
       </c>
       <c r="C14">
-        <v>684.4028437057481</v>
+        <v>678.439358497057</v>
       </c>
       <c r="D14">
-        <v>651.9452437057481</v>
+        <v>653.5519584970571</v>
       </c>
       <c r="E14">
-        <v>85.8224</v>
+        <v>93.3926</v>
       </c>
       <c r="F14">
-        <v>90.8424</v>
+        <v>98.4126</v>
       </c>
       <c r="G14">
         <v>123.3</v>
@@ -2435,28 +2435,28 @@
         <v>41.4</v>
       </c>
       <c r="M14">
-        <v>4.860068399999999</v>
+        <v>5.2650741</v>
       </c>
       <c r="N14">
-        <v>36.5399316</v>
+        <v>36.1349259</v>
       </c>
       <c r="O14">
-        <v>9.134982900000001</v>
+        <v>9.033731475</v>
       </c>
       <c r="P14">
-        <v>27.4049487</v>
+        <v>27.101194425</v>
       </c>
       <c r="Q14">
-        <v>50.8049487</v>
+        <v>50.50119442499999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08291122826808134</v>
+        <v>0.08324104721820648</v>
       </c>
       <c r="T14">
-        <v>0.7233669140377558</v>
+        <v>0.7297956992673839</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.51839862994521</v>
+        <v>7.8631371968725</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07763596107983964</v>
+        <v>0.07757904128376769</v>
       </c>
       <c r="C15">
-        <v>678.439358497057</v>
+        <v>671.5203843807003</v>
       </c>
       <c r="D15">
-        <v>653.5519584970571</v>
+        <v>654.2031843807003</v>
       </c>
       <c r="E15">
-        <v>93.3926</v>
+        <v>100.9628</v>
       </c>
       <c r="F15">
-        <v>98.4126</v>
+        <v>105.9828</v>
       </c>
       <c r="G15">
         <v>123.3</v>
@@ -2517,45 +2517,45 @@
         <v>41.4</v>
       </c>
       <c r="M15">
-        <v>5.2650741</v>
+        <v>5.75486604</v>
       </c>
       <c r="N15">
-        <v>36.1349259</v>
+        <v>35.64513396</v>
       </c>
       <c r="O15">
-        <v>9.033731475</v>
+        <v>8.911283489999999</v>
       </c>
       <c r="P15">
-        <v>27.101194425</v>
+        <v>26.73385047</v>
       </c>
       <c r="Q15">
-        <v>50.50119442499999</v>
+        <v>50.13385047</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08324104721820648</v>
+        <v>0.08357853637647407</v>
       </c>
       <c r="T15">
-        <v>0.7297956992673839</v>
+        <v>0.7363739911302591</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.8631371968725</v>
+        <v>7.193912023710633</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07757904128376769</v>
+        <v>0.07744412148769576</v>
       </c>
       <c r="C16">
-        <v>671.5203843807003</v>
+        <v>665.4990135054609</v>
       </c>
       <c r="D16">
-        <v>654.2031843807003</v>
+        <v>655.7520135054609</v>
       </c>
       <c r="E16">
-        <v>100.9628</v>
+        <v>108.533</v>
       </c>
       <c r="F16">
-        <v>105.9828</v>
+        <v>113.553</v>
       </c>
       <c r="G16">
         <v>123.3</v>
@@ -2599,28 +2599,28 @@
         <v>41.4</v>
       </c>
       <c r="M16">
-        <v>5.75486604</v>
+        <v>6.165927900000001</v>
       </c>
       <c r="N16">
-        <v>35.64513396</v>
+        <v>35.2340721</v>
       </c>
       <c r="O16">
-        <v>8.911283489999999</v>
+        <v>8.808518025</v>
       </c>
       <c r="P16">
-        <v>26.73385047</v>
+        <v>26.425554075</v>
       </c>
       <c r="Q16">
-        <v>50.13385047</v>
+        <v>49.825554075</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08357853637647407</v>
+        <v>0.08392396645611266</v>
       </c>
       <c r="T16">
-        <v>0.7363739911302591</v>
+        <v>0.7431070663310845</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.193912023710633</v>
+        <v>6.71431788879659</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07744412148769576</v>
+        <v>0.07730920169162382</v>
       </c>
       <c r="C17">
-        <v>665.4990135054609</v>
+        <v>659.48499375456</v>
       </c>
       <c r="D17">
-        <v>655.7520135054609</v>
+        <v>657.3081937545601</v>
       </c>
       <c r="E17">
-        <v>108.533</v>
+        <v>116.1032</v>
       </c>
       <c r="F17">
-        <v>113.553</v>
+        <v>121.1232</v>
       </c>
       <c r="G17">
         <v>123.3</v>
@@ -2681,28 +2681,28 @@
         <v>41.4</v>
       </c>
       <c r="M17">
-        <v>6.1659279</v>
+        <v>6.57698976</v>
       </c>
       <c r="N17">
-        <v>35.2340721</v>
+        <v>34.82301024</v>
       </c>
       <c r="O17">
-        <v>8.808518025</v>
+        <v>8.705752560000001</v>
       </c>
       <c r="P17">
-        <v>26.425554075</v>
+        <v>26.11725768</v>
       </c>
       <c r="Q17">
-        <v>49.825554075</v>
+        <v>49.51725768</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08392396645611266</v>
+        <v>0.08427762106145693</v>
       </c>
       <c r="T17">
-        <v>0.7431070663310845</v>
+        <v>0.7500004528462151</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.714317888796591</v>
+        <v>6.294673020746805</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07730920169162382</v>
+        <v>0.07730178189555188</v>
       </c>
       <c r="C18">
-        <v>659.48499375456</v>
+        <v>652.0005888156601</v>
       </c>
       <c r="D18">
-        <v>657.3081937545601</v>
+        <v>657.3939888156601</v>
       </c>
       <c r="E18">
-        <v>116.1032</v>
+        <v>123.6734</v>
       </c>
       <c r="F18">
-        <v>121.1232</v>
+        <v>128.6934</v>
       </c>
       <c r="G18">
         <v>123.3</v>
@@ -2763,45 +2763,45 @@
         <v>41.4</v>
       </c>
       <c r="M18">
-        <v>6.57698976</v>
+        <v>7.11674502</v>
       </c>
       <c r="N18">
-        <v>34.82301024</v>
+        <v>34.28325498</v>
       </c>
       <c r="O18">
-        <v>8.705752560000001</v>
+        <v>8.570813744999999</v>
       </c>
       <c r="P18">
-        <v>26.11725768</v>
+        <v>25.712441235</v>
       </c>
       <c r="Q18">
-        <v>49.51725768</v>
+        <v>49.11244123499999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08427762106145693</v>
+        <v>0.08463979746452036</v>
       </c>
       <c r="T18">
-        <v>0.7500004528462151</v>
+        <v>0.7570599450605057</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.294673020746805</v>
+        <v>5.817266163626022</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07730178189555188</v>
+        <v>0.07717436209947995</v>
       </c>
       <c r="C19">
-        <v>652.0005888156601</v>
+        <v>645.9072458958327</v>
       </c>
       <c r="D19">
-        <v>657.3939888156601</v>
+        <v>658.8708458958328</v>
       </c>
       <c r="E19">
-        <v>123.6734</v>
+        <v>131.2436</v>
       </c>
       <c r="F19">
-        <v>128.6934</v>
+        <v>136.2636</v>
       </c>
       <c r="G19">
         <v>123.3</v>
@@ -2845,28 +2845,28 @@
         <v>41.4</v>
       </c>
       <c r="M19">
-        <v>7.11674502</v>
+        <v>7.535377080000002</v>
       </c>
       <c r="N19">
-        <v>34.28325498</v>
+        <v>33.86462292</v>
       </c>
       <c r="O19">
-        <v>8.570813744999999</v>
+        <v>8.466155729999999</v>
       </c>
       <c r="P19">
-        <v>25.712441235</v>
+        <v>25.39846719</v>
       </c>
       <c r="Q19">
-        <v>49.11244123499999</v>
+        <v>48.79846719</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08463979746452036</v>
+        <v>0.08501080743839018</v>
       </c>
       <c r="T19">
-        <v>0.7570599450605057</v>
+        <v>0.7642916200117299</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.817266163626022</v>
+        <v>5.494084710091242</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07717436209947995</v>
+        <v>0.07704694230340803</v>
       </c>
       <c r="C20">
-        <v>645.9072458958327</v>
+        <v>639.8205535320884</v>
       </c>
       <c r="D20">
-        <v>658.8708458958328</v>
+        <v>660.3543535320885</v>
       </c>
       <c r="E20">
-        <v>131.2436</v>
+        <v>138.8138</v>
       </c>
       <c r="F20">
-        <v>136.2636</v>
+        <v>143.8338</v>
       </c>
       <c r="G20">
         <v>123.3</v>
@@ -2927,28 +2927,28 @@
         <v>41.4</v>
       </c>
       <c r="M20">
-        <v>7.53537708</v>
+        <v>7.95400914</v>
       </c>
       <c r="N20">
-        <v>33.86462292</v>
+        <v>33.44599085999999</v>
       </c>
       <c r="O20">
-        <v>8.466155730000001</v>
+        <v>8.361497714999999</v>
       </c>
       <c r="P20">
-        <v>25.39846719</v>
+        <v>25.084493145</v>
       </c>
       <c r="Q20">
-        <v>48.79846719</v>
+        <v>48.48449314499999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08501080743839018</v>
+        <v>0.08539097815235558</v>
       </c>
       <c r="T20">
-        <v>0.7642916200117299</v>
+        <v>0.7717018548382932</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.494084710091244</v>
+        <v>5.204922356928545</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07704694230340803</v>
+        <v>0.07691952250733608</v>
       </c>
       <c r="C21">
-        <v>639.8205535320884</v>
+        <v>633.7405567487998</v>
       </c>
       <c r="D21">
-        <v>660.3543535320885</v>
+        <v>661.8445567487998</v>
       </c>
       <c r="E21">
-        <v>138.8138</v>
+        <v>146.384</v>
       </c>
       <c r="F21">
-        <v>143.8338</v>
+        <v>151.404</v>
       </c>
       <c r="G21">
         <v>123.3</v>
@@ -3009,28 +3009,28 @@
         <v>41.4</v>
       </c>
       <c r="M21">
-        <v>7.95400914</v>
+        <v>8.3726412</v>
       </c>
       <c r="N21">
-        <v>33.44599085999999</v>
+        <v>33.0273588</v>
       </c>
       <c r="O21">
-        <v>8.361497714999999</v>
+        <v>8.2568397</v>
       </c>
       <c r="P21">
-        <v>25.084493145</v>
+        <v>24.7705191</v>
       </c>
       <c r="Q21">
-        <v>48.48449314499999</v>
+        <v>48.1705191</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08539097815235558</v>
+        <v>0.0857806531341701</v>
       </c>
       <c r="T21">
-        <v>0.7717018548382932</v>
+        <v>0.7792973455355204</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.204922356928545</v>
+        <v>4.944676239082119</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07691952250733608</v>
+        <v>0.07679210271126415</v>
       </c>
       <c r="C22">
-        <v>633.7405567487998</v>
+        <v>627.6673009776788</v>
       </c>
       <c r="D22">
-        <v>661.8445567487998</v>
+        <v>663.3415009776788</v>
       </c>
       <c r="E22">
-        <v>146.384</v>
+        <v>153.9542</v>
       </c>
       <c r="F22">
-        <v>151.404</v>
+        <v>158.9742</v>
       </c>
       <c r="G22">
         <v>123.3</v>
@@ -3091,28 +3091,28 @@
         <v>41.4</v>
       </c>
       <c r="M22">
-        <v>8.3726412</v>
+        <v>8.791273260000002</v>
       </c>
       <c r="N22">
-        <v>33.0273588</v>
+        <v>32.60872673999999</v>
       </c>
       <c r="O22">
-        <v>8.2568397</v>
+        <v>8.152181684999999</v>
       </c>
       <c r="P22">
-        <v>24.7705191</v>
+        <v>24.456545055</v>
       </c>
       <c r="Q22">
-        <v>48.1705191</v>
+        <v>47.856545055</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0857806531341701</v>
+        <v>0.08618019330539764</v>
       </c>
       <c r="T22">
-        <v>0.7792973455355204</v>
+        <v>0.7870851271364749</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.944676239082119</v>
+        <v>4.709215465792493</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07679210271126415</v>
+        <v>0.07707718291519221</v>
       </c>
       <c r="C23">
-        <v>627.6673009776788</v>
+        <v>616.7572675526739</v>
       </c>
       <c r="D23">
-        <v>663.3415009776788</v>
+        <v>660.0016675526739</v>
       </c>
       <c r="E23">
-        <v>153.9542</v>
+        <v>161.5244</v>
       </c>
       <c r="F23">
-        <v>158.9742</v>
+        <v>166.5444</v>
       </c>
       <c r="G23">
         <v>123.3</v>
@@ -3173,45 +3173,45 @@
         <v>41.4</v>
       </c>
       <c r="M23">
-        <v>8.791273260000001</v>
+        <v>9.626266320000001</v>
       </c>
       <c r="N23">
-        <v>32.60872673999999</v>
+        <v>31.77373368</v>
       </c>
       <c r="O23">
-        <v>8.152181684999999</v>
+        <v>7.94343342</v>
       </c>
       <c r="P23">
-        <v>24.456545055</v>
+        <v>23.83030026</v>
       </c>
       <c r="Q23">
-        <v>47.856545055</v>
+        <v>47.23030026</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08618019330539764</v>
+        <v>0.08658997809640026</v>
       </c>
       <c r="T23">
-        <v>0.7870851271364749</v>
+        <v>0.7950725954451463</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.709215465792493</v>
+        <v>4.300732872306404</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07707718291519221</v>
+        <v>0.07696851311912026</v>
       </c>
       <c r="C24">
-        <v>616.7572675526739</v>
+        <v>610.4562053495961</v>
       </c>
       <c r="D24">
-        <v>660.0016675526739</v>
+        <v>661.2708053495961</v>
       </c>
       <c r="E24">
-        <v>161.5244</v>
+        <v>169.0946</v>
       </c>
       <c r="F24">
-        <v>166.5444</v>
+        <v>174.1146</v>
       </c>
       <c r="G24">
         <v>123.3</v>
@@ -3255,28 +3255,28 @@
         <v>41.4</v>
       </c>
       <c r="M24">
-        <v>9.626266320000001</v>
+        <v>10.06382388</v>
       </c>
       <c r="N24">
-        <v>31.77373368</v>
+        <v>31.33617612</v>
       </c>
       <c r="O24">
-        <v>7.94343342</v>
+        <v>7.834044029999999</v>
       </c>
       <c r="P24">
-        <v>23.83030026</v>
+        <v>23.50213209</v>
       </c>
       <c r="Q24">
-        <v>47.23030026</v>
+        <v>46.90213208999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08658997809640026</v>
+        <v>0.08701040664820814</v>
       </c>
       <c r="T24">
-        <v>0.7950725954451463</v>
+        <v>0.8032675304631338</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.300732872306404</v>
+        <v>4.113744486553951</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07696851311912026</v>
+        <v>0.07748984332304834</v>
       </c>
       <c r="C25">
-        <v>610.4562053495961</v>
+        <v>596.8415229572164</v>
       </c>
       <c r="D25">
-        <v>661.2708053495961</v>
+        <v>655.2263229572164</v>
       </c>
       <c r="E25">
-        <v>169.0946</v>
+        <v>176.6648</v>
       </c>
       <c r="F25">
-        <v>174.1146</v>
+        <v>181.6848</v>
       </c>
       <c r="G25">
         <v>123.3</v>
@@ -3337,45 +3337,45 @@
         <v>41.4</v>
       </c>
       <c r="M25">
-        <v>10.06382388</v>
+        <v>11.13727824</v>
       </c>
       <c r="N25">
-        <v>31.33617612</v>
+        <v>30.26272176</v>
       </c>
       <c r="O25">
-        <v>7.834044029999999</v>
+        <v>7.56568044</v>
       </c>
       <c r="P25">
-        <v>23.50213209</v>
+        <v>22.69704132</v>
       </c>
       <c r="Q25">
-        <v>46.90213208999999</v>
+        <v>46.09704132</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08701040664820814</v>
+        <v>0.08744189910927412</v>
       </c>
       <c r="T25">
-        <v>0.8032675304631338</v>
+        <v>0.8116781216658052</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.113744486553951</v>
+        <v>3.717245731664507</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07748984332304834</v>
+        <v>0.07740742352697638</v>
       </c>
       <c r="C26">
-        <v>596.8415229572164</v>
+        <v>590.2195619411959</v>
       </c>
       <c r="D26">
-        <v>655.2263229572164</v>
+        <v>656.174561941196</v>
       </c>
       <c r="E26">
-        <v>176.6648</v>
+        <v>184.235</v>
       </c>
       <c r="F26">
-        <v>181.6848</v>
+        <v>189.255</v>
       </c>
       <c r="G26">
         <v>123.3</v>
@@ -3419,28 +3419,28 @@
         <v>41.4</v>
       </c>
       <c r="M26">
-        <v>11.13727824</v>
+        <v>11.6013315</v>
       </c>
       <c r="N26">
-        <v>30.26272176</v>
+        <v>29.7986685</v>
       </c>
       <c r="O26">
-        <v>7.56568044</v>
+        <v>7.449667125</v>
       </c>
       <c r="P26">
-        <v>22.69704132</v>
+        <v>22.349001375</v>
       </c>
       <c r="Q26">
-        <v>46.09704132</v>
+        <v>45.749001375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08744189910927412</v>
+        <v>0.08788489803596852</v>
       </c>
       <c r="T26">
-        <v>0.8116781216658052</v>
+        <v>0.8203129953005478</v>
       </c>
       <c r="U26">
         <v>0.0613</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.717245731664507</v>
+        <v>3.568555902397927</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07740742352697638</v>
+        <v>0.07787100373090446</v>
       </c>
       <c r="C27">
-        <v>590.2195619411959</v>
+        <v>577.3512833453306</v>
       </c>
       <c r="D27">
-        <v>656.174561941196</v>
+        <v>650.8764833453306</v>
       </c>
       <c r="E27">
-        <v>184.235</v>
+        <v>191.8052</v>
       </c>
       <c r="F27">
-        <v>189.255</v>
+        <v>196.8252</v>
       </c>
       <c r="G27">
         <v>123.3</v>
@@ -3501,45 +3501,45 @@
         <v>41.4</v>
       </c>
       <c r="M27">
-        <v>11.6013315</v>
+        <v>12.61649532</v>
       </c>
       <c r="N27">
-        <v>29.7986685</v>
+        <v>28.78350468</v>
       </c>
       <c r="O27">
-        <v>7.449667125</v>
+        <v>7.19587617</v>
       </c>
       <c r="P27">
-        <v>22.349001375</v>
+        <v>21.58762851</v>
       </c>
       <c r="Q27">
-        <v>45.749001375</v>
+        <v>44.98762851</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08788489803596852</v>
+        <v>0.08833986990662765</v>
       </c>
       <c r="T27">
-        <v>0.8203129953005478</v>
+        <v>0.8291812438983917</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.568555902397927</v>
+        <v>3.281418408991254</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07787100373090446</v>
+        <v>0.07780958393483252</v>
       </c>
       <c r="C28">
-        <v>577.3512833453306</v>
+        <v>570.478104421854</v>
       </c>
       <c r="D28">
-        <v>650.8764833453306</v>
+        <v>651.5735044218541</v>
       </c>
       <c r="E28">
-        <v>191.8052</v>
+        <v>199.3754</v>
       </c>
       <c r="F28">
-        <v>196.8252</v>
+        <v>204.3954</v>
       </c>
       <c r="G28">
         <v>123.3</v>
@@ -3583,28 +3583,28 @@
         <v>41.4</v>
       </c>
       <c r="M28">
-        <v>12.61649532</v>
+        <v>13.10174514</v>
       </c>
       <c r="N28">
-        <v>28.78350468</v>
+        <v>28.29825486</v>
       </c>
       <c r="O28">
-        <v>7.19587617</v>
+        <v>7.074563715</v>
       </c>
       <c r="P28">
-        <v>21.58762851</v>
+        <v>21.223691145</v>
       </c>
       <c r="Q28">
-        <v>44.98762851</v>
+        <v>44.623691145</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08833986990662765</v>
+        <v>0.08880730676004456</v>
       </c>
       <c r="T28">
-        <v>0.8291812438983917</v>
+        <v>0.8382924582112448</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.281418408991254</v>
+        <v>3.15988439384343</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07780958393483252</v>
+        <v>0.07774816413876058</v>
       </c>
       <c r="C29">
-        <v>570.478104421854</v>
+        <v>563.6064199730858</v>
       </c>
       <c r="D29">
-        <v>651.5735044218541</v>
+        <v>652.2720199730859</v>
       </c>
       <c r="E29">
-        <v>199.3754</v>
+        <v>206.9456</v>
       </c>
       <c r="F29">
-        <v>204.3954</v>
+        <v>211.9656</v>
       </c>
       <c r="G29">
         <v>123.3</v>
@@ -3665,28 +3665,28 @@
         <v>41.4</v>
       </c>
       <c r="M29">
-        <v>13.10174514</v>
+        <v>13.58699496</v>
       </c>
       <c r="N29">
-        <v>28.29825486</v>
+        <v>27.81300504</v>
       </c>
       <c r="O29">
-        <v>7.074563715</v>
+        <v>6.953251259999999</v>
       </c>
       <c r="P29">
-        <v>21.223691145</v>
+        <v>20.85975378</v>
       </c>
       <c r="Q29">
-        <v>44.623691145</v>
+        <v>44.25975378</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08880730676004456</v>
+        <v>0.08928772797050082</v>
       </c>
       <c r="T29">
-        <v>0.8382924582112448</v>
+        <v>0.8476567618105662</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.15988439384343</v>
+        <v>3.047031379777593</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07774816413876058</v>
+        <v>0.07938324434268865</v>
       </c>
       <c r="C30">
-        <v>563.6064199730858</v>
+        <v>537.9373603486296</v>
       </c>
       <c r="D30">
-        <v>652.2720199730859</v>
+        <v>634.1731603486296</v>
       </c>
       <c r="E30">
-        <v>206.9456</v>
+        <v>214.5158</v>
       </c>
       <c r="F30">
-        <v>211.9656</v>
+        <v>219.5358</v>
       </c>
       <c r="G30">
         <v>123.3</v>
@@ -3747,45 +3747,45 @@
         <v>41.4</v>
       </c>
       <c r="M30">
-        <v>13.58699496</v>
+        <v>15.78462402</v>
       </c>
       <c r="N30">
-        <v>27.81300504</v>
+        <v>25.61537598</v>
       </c>
       <c r="O30">
-        <v>6.953251259999999</v>
+        <v>6.403843994999999</v>
       </c>
       <c r="P30">
-        <v>20.85975378</v>
+        <v>19.211531985</v>
       </c>
       <c r="Q30">
-        <v>44.25975378</v>
+        <v>42.611531985</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08928772797050082</v>
+        <v>0.08978168217280091</v>
       </c>
       <c r="T30">
-        <v>0.8476567618105662</v>
+        <v>0.8572848486098682</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.047031379777593</v>
+        <v>2.622805582669811</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07938324434268865</v>
+        <v>0.0793803245466167</v>
       </c>
       <c r="C31">
-        <v>537.9373603486296</v>
+        <v>530.3985846259626</v>
       </c>
       <c r="D31">
-        <v>634.1731603486296</v>
+        <v>634.2045846259626</v>
       </c>
       <c r="E31">
-        <v>214.5158</v>
+        <v>222.086</v>
       </c>
       <c r="F31">
-        <v>219.5358</v>
+        <v>227.106</v>
       </c>
       <c r="G31">
         <v>123.3</v>
@@ -3829,28 +3829,28 @@
         <v>41.4</v>
       </c>
       <c r="M31">
-        <v>15.78462402</v>
+        <v>16.3289214</v>
       </c>
       <c r="N31">
-        <v>25.61537598</v>
+        <v>25.0710786</v>
       </c>
       <c r="O31">
-        <v>6.403843995</v>
+        <v>6.267769649999999</v>
       </c>
       <c r="P31">
-        <v>19.211531985</v>
+        <v>18.80330895</v>
       </c>
       <c r="Q31">
-        <v>42.611531985</v>
+        <v>42.20330894999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08978168217280091</v>
+        <v>0.09028974935230959</v>
       </c>
       <c r="T31">
-        <v>0.8572848486098682</v>
+        <v>0.8671880236034363</v>
       </c>
       <c r="U31">
         <v>0.07190000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.622805582669812</v>
+        <v>2.535378729914151</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0793803245466167</v>
+        <v>0.08028415475054476</v>
       </c>
       <c r="C32">
-        <v>530.3985846259626</v>
+        <v>513.2473996225743</v>
       </c>
       <c r="D32">
-        <v>634.2045846259626</v>
+        <v>624.6235996225744</v>
       </c>
       <c r="E32">
-        <v>222.086</v>
+        <v>229.6562</v>
       </c>
       <c r="F32">
-        <v>227.106</v>
+        <v>234.6762</v>
       </c>
       <c r="G32">
         <v>123.3</v>
@@ -3911,45 +3911,45 @@
         <v>41.4</v>
       </c>
       <c r="M32">
-        <v>16.3289214</v>
+        <v>17.78845596</v>
       </c>
       <c r="N32">
-        <v>25.0710786</v>
+        <v>23.61154404</v>
       </c>
       <c r="O32">
-        <v>6.267769649999999</v>
+        <v>5.90288601</v>
       </c>
       <c r="P32">
-        <v>18.80330895</v>
+        <v>17.70865803</v>
       </c>
       <c r="Q32">
-        <v>42.20330894999999</v>
+        <v>41.10865803</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09028974935230959</v>
+        <v>0.09081254311673155</v>
       </c>
       <c r="T32">
-        <v>0.8671880236034363</v>
+        <v>0.8773782471475424</v>
       </c>
       <c r="U32">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.535378729914151</v>
+        <v>2.327352081208964</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08028415475054476</v>
+        <v>0.08031048495447282</v>
       </c>
       <c r="C33">
-        <v>513.2473996225743</v>
+        <v>505.4024257372</v>
       </c>
       <c r="D33">
-        <v>624.6235996225744</v>
+        <v>624.3488257372001</v>
       </c>
       <c r="E33">
-        <v>229.6562</v>
+        <v>237.2264</v>
       </c>
       <c r="F33">
-        <v>234.6762</v>
+        <v>242.2464</v>
       </c>
       <c r="G33">
         <v>123.3</v>
@@ -3993,28 +3993,28 @@
         <v>41.4</v>
       </c>
       <c r="M33">
-        <v>17.78845596</v>
+        <v>18.36227712</v>
       </c>
       <c r="N33">
-        <v>23.61154404</v>
+        <v>23.03772288</v>
       </c>
       <c r="O33">
-        <v>5.90288601</v>
+        <v>5.759430719999999</v>
       </c>
       <c r="P33">
-        <v>17.70865803</v>
+        <v>17.27829216</v>
       </c>
       <c r="Q33">
-        <v>41.10865803</v>
+        <v>40.67829216</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09081254311673155</v>
+        <v>0.0913507131683424</v>
       </c>
       <c r="T33">
-        <v>0.8773782471475424</v>
+        <v>0.8878681831488282</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.327352081208964</v>
+        <v>2.254622328671184</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08031048495447282</v>
+        <v>0.0803368151584009</v>
       </c>
       <c r="C34">
-        <v>505.4024257372</v>
+        <v>497.5576934933188</v>
       </c>
       <c r="D34">
-        <v>624.3488257372001</v>
+        <v>624.0742934933188</v>
       </c>
       <c r="E34">
-        <v>237.2264</v>
+        <v>244.7966</v>
       </c>
       <c r="F34">
-        <v>242.2464</v>
+        <v>249.8166</v>
       </c>
       <c r="G34">
         <v>123.3</v>
@@ -4075,28 +4075,28 @@
         <v>41.4</v>
       </c>
       <c r="M34">
-        <v>18.36227712</v>
+        <v>18.93609828</v>
       </c>
       <c r="N34">
-        <v>23.03772288</v>
+        <v>22.46390172</v>
       </c>
       <c r="O34">
-        <v>5.759430719999999</v>
+        <v>5.61597543</v>
       </c>
       <c r="P34">
-        <v>17.27829216</v>
+        <v>16.84792629</v>
       </c>
       <c r="Q34">
-        <v>40.67829216</v>
+        <v>40.24792629</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0913507131683424</v>
+        <v>0.09190494799761328</v>
       </c>
       <c r="T34">
-        <v>0.8878681831488282</v>
+        <v>0.8986712515680629</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.254622328671184</v>
+        <v>2.186300439923572</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0803368151584009</v>
+        <v>0.08036314536232896</v>
       </c>
       <c r="C35">
-        <v>497.5576934933188</v>
+        <v>489.7132025723149</v>
       </c>
       <c r="D35">
-        <v>624.0742934933188</v>
+        <v>623.800002572315</v>
       </c>
       <c r="E35">
-        <v>244.7966</v>
+        <v>252.3668</v>
       </c>
       <c r="F35">
-        <v>249.8166</v>
+        <v>257.3868</v>
       </c>
       <c r="G35">
         <v>123.3</v>
@@ -4157,28 +4157,28 @@
         <v>41.4</v>
       </c>
       <c r="M35">
-        <v>18.93609828</v>
+        <v>19.50991944</v>
       </c>
       <c r="N35">
-        <v>22.46390172</v>
+        <v>21.89008056</v>
       </c>
       <c r="O35">
-        <v>5.61597543</v>
+        <v>5.472520139999999</v>
       </c>
       <c r="P35">
-        <v>16.84792629</v>
+        <v>16.41756042</v>
       </c>
       <c r="Q35">
-        <v>40.24792629</v>
+        <v>39.81756041999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09190494799761328</v>
+        <v>0.09247597782171055</v>
       </c>
       <c r="T35">
-        <v>0.8986712515680629</v>
+        <v>0.9098016856969713</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.186300439923572</v>
+        <v>2.121997485808173</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08036314536232896</v>
+        <v>0.08038947556625702</v>
       </c>
       <c r="C36">
-        <v>489.7132025723149</v>
+        <v>481.8689526561318</v>
       </c>
       <c r="D36">
-        <v>623.800002572315</v>
+        <v>623.5259526561318</v>
       </c>
       <c r="E36">
-        <v>252.3668</v>
+        <v>259.937</v>
       </c>
       <c r="F36">
-        <v>257.3868</v>
+        <v>264.957</v>
       </c>
       <c r="G36">
         <v>123.3</v>
@@ -4239,28 +4239,28 @@
         <v>41.4</v>
       </c>
       <c r="M36">
-        <v>19.50991944</v>
+        <v>20.0837406</v>
       </c>
       <c r="N36">
-        <v>21.89008056</v>
+        <v>21.3162594</v>
       </c>
       <c r="O36">
-        <v>5.472520139999999</v>
+        <v>5.329064849999999</v>
       </c>
       <c r="P36">
-        <v>16.41756042</v>
+        <v>15.98719455</v>
       </c>
       <c r="Q36">
-        <v>39.81756041999999</v>
+        <v>39.38719455</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09247597782171055</v>
+        <v>0.09306457779424157</v>
       </c>
       <c r="T36">
-        <v>0.9098016856969713</v>
+        <v>0.9212745947221538</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.121997485808173</v>
+        <v>2.061368986213654</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08038947556625702</v>
+        <v>0.08041580577018509</v>
       </c>
       <c r="C37">
-        <v>481.8689526561318</v>
+        <v>474.0249434272716</v>
       </c>
       <c r="D37">
-        <v>623.5259526561318</v>
+        <v>623.2521434272717</v>
       </c>
       <c r="E37">
-        <v>259.937</v>
+        <v>267.5072000000001</v>
       </c>
       <c r="F37">
-        <v>264.957</v>
+        <v>272.5272000000001</v>
       </c>
       <c r="G37">
         <v>123.3</v>
@@ -4321,28 +4321,28 @@
         <v>41.4</v>
       </c>
       <c r="M37">
-        <v>20.0837406</v>
+        <v>20.65756176000001</v>
       </c>
       <c r="N37">
-        <v>21.3162594</v>
+        <v>20.74243823999999</v>
       </c>
       <c r="O37">
-        <v>5.329064849999999</v>
+        <v>5.185609559999998</v>
       </c>
       <c r="P37">
-        <v>15.98719455</v>
+        <v>15.55682867999999</v>
       </c>
       <c r="Q37">
-        <v>39.38719455</v>
+        <v>38.95682867999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09306457779424157</v>
+        <v>0.09367157151591421</v>
       </c>
       <c r="T37">
-        <v>0.9212745947221538</v>
+        <v>0.9331060321543732</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.061368986213654</v>
+        <v>2.004108736596607</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0804158057701851</v>
+        <v>0.08438263597411315</v>
       </c>
       <c r="C38">
-        <v>474.0249434272715</v>
+        <v>427.7802074542944</v>
       </c>
       <c r="D38">
-        <v>623.2521434272716</v>
+        <v>584.5776074542945</v>
       </c>
       <c r="E38">
-        <v>267.5072</v>
+        <v>275.0774</v>
       </c>
       <c r="F38">
-        <v>272.5272</v>
+        <v>280.0974</v>
       </c>
       <c r="G38">
         <v>123.3</v>
@@ -4403,45 +4403,45 @@
         <v>41.4</v>
       </c>
       <c r="M38">
-        <v>20.65756176</v>
+        <v>25.208766</v>
       </c>
       <c r="N38">
-        <v>20.74243824</v>
+        <v>16.191234</v>
       </c>
       <c r="O38">
-        <v>5.18560956</v>
+        <v>4.0478085</v>
       </c>
       <c r="P38">
-        <v>15.55682868</v>
+        <v>12.1434255</v>
       </c>
       <c r="Q38">
-        <v>38.95682868</v>
+        <v>35.5434255</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09367157151591421</v>
+        <v>0.09429783487954468</v>
       </c>
       <c r="T38">
-        <v>0.9331060321543732</v>
+        <v>0.945313070774917</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.004108736596608</v>
+        <v>1.642285861989437</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08438263597411315</v>
+        <v>0.08451546617804122</v>
       </c>
       <c r="C39">
-        <v>427.7802074542944</v>
+        <v>418.9978605098456</v>
       </c>
       <c r="D39">
-        <v>584.5776074542945</v>
+        <v>583.3654605098457</v>
       </c>
       <c r="E39">
-        <v>275.0774</v>
+        <v>282.6476</v>
       </c>
       <c r="F39">
-        <v>280.0974</v>
+        <v>287.6676</v>
       </c>
       <c r="G39">
         <v>123.3</v>
@@ -4485,28 +4485,28 @@
         <v>41.4</v>
       </c>
       <c r="M39">
-        <v>25.208766</v>
+        <v>25.890084</v>
       </c>
       <c r="N39">
-        <v>16.191234</v>
+        <v>15.509916</v>
       </c>
       <c r="O39">
-        <v>4.0478085</v>
+        <v>3.877479</v>
       </c>
       <c r="P39">
-        <v>12.1434255</v>
+        <v>11.632437</v>
       </c>
       <c r="Q39">
-        <v>35.5434255</v>
+        <v>35.032437</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09429783487954468</v>
+        <v>0.09494430028716325</v>
       </c>
       <c r="T39">
-        <v>0.945313070774917</v>
+        <v>0.9579138848348333</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.642285861989437</v>
+        <v>1.599067812989714</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08451546617804122</v>
+        <v>0.08464829638196927</v>
       </c>
       <c r="C40">
-        <v>418.9978605098456</v>
+        <v>410.2205300417141</v>
       </c>
       <c r="D40">
-        <v>583.3654605098457</v>
+        <v>582.1583300417142</v>
       </c>
       <c r="E40">
-        <v>282.6476</v>
+        <v>290.2178</v>
       </c>
       <c r="F40">
-        <v>287.6676</v>
+        <v>295.2378</v>
       </c>
       <c r="G40">
         <v>123.3</v>
@@ -4567,28 +4567,28 @@
         <v>41.4</v>
       </c>
       <c r="M40">
-        <v>25.890084</v>
+        <v>26.571402</v>
       </c>
       <c r="N40">
-        <v>15.509916</v>
+        <v>14.828598</v>
       </c>
       <c r="O40">
-        <v>3.877479</v>
+        <v>3.7071495</v>
       </c>
       <c r="P40">
-        <v>11.632437</v>
+        <v>11.1214485</v>
       </c>
       <c r="Q40">
-        <v>35.032437</v>
+        <v>34.5214485</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09494430028716325</v>
+        <v>0.09561196128191685</v>
       </c>
       <c r="T40">
-        <v>0.9579138848348333</v>
+        <v>0.9709278403393369</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.599067812989714</v>
+        <v>1.558066074195106</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08464829638196927</v>
+        <v>0.08478112658589734</v>
       </c>
       <c r="C41">
-        <v>410.2205300417141</v>
+        <v>401.4481849731363</v>
       </c>
       <c r="D41">
-        <v>582.1583300417142</v>
+        <v>580.9561849731364</v>
       </c>
       <c r="E41">
-        <v>290.2178</v>
+        <v>297.788</v>
       </c>
       <c r="F41">
-        <v>295.2378</v>
+        <v>302.808</v>
       </c>
       <c r="G41">
         <v>123.3</v>
@@ -4649,28 +4649,28 @@
         <v>41.4</v>
       </c>
       <c r="M41">
-        <v>26.571402</v>
+        <v>27.25272</v>
       </c>
       <c r="N41">
-        <v>14.828598</v>
+        <v>14.14728</v>
       </c>
       <c r="O41">
-        <v>3.7071495</v>
+        <v>3.53682</v>
       </c>
       <c r="P41">
-        <v>11.1214485</v>
+        <v>10.61046</v>
       </c>
       <c r="Q41">
-        <v>34.5214485</v>
+        <v>34.01045999999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09561196128191685</v>
+        <v>0.09630187764316223</v>
       </c>
       <c r="T41">
-        <v>0.9709278403393369</v>
+        <v>0.9843755943606574</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.558066074195106</v>
+        <v>1.519114422340229</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08478112658589734</v>
+        <v>0.1040702702074271</v>
       </c>
       <c r="C42">
-        <v>401.4481849731363</v>
+        <v>259.8561392940475</v>
       </c>
       <c r="D42">
-        <v>580.9561849731364</v>
+        <v>446.9343392940475</v>
       </c>
       <c r="E42">
-        <v>297.788</v>
+        <v>305.3582</v>
       </c>
       <c r="F42">
-        <v>302.808</v>
+        <v>310.3782</v>
       </c>
       <c r="G42">
         <v>123.3</v>
@@ -4731,45 +4731,45 @@
         <v>41.4</v>
       </c>
       <c r="M42">
-        <v>27.25272</v>
+        <v>45.56351976000001</v>
       </c>
       <c r="N42">
-        <v>14.14728</v>
+        <v>-4.163519760000007</v>
       </c>
       <c r="O42">
-        <v>3.53682</v>
+        <v>-1.040879940000002</v>
       </c>
       <c r="P42">
-        <v>10.61046</v>
+        <v>-3.122639820000005</v>
       </c>
       <c r="Q42">
-        <v>34.01045999999999</v>
+        <v>20.27736018</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09630187764316223</v>
+        <v>0.09754966103133755</v>
       </c>
       <c r="T42">
-        <v>0.9843755943606574</v>
+        <v>1.008697215094193</v>
       </c>
       <c r="U42">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.25</v>
+        <v>0.2271554097338682</v>
       </c>
       <c r="W42">
-        <v>0.0675</v>
+        <v>0.1134535858510682</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.519114422340229</v>
+        <v>0.9086216389354727</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1040702702074271</v>
+        <v>0.1050802702074271</v>
       </c>
       <c r="C43">
-        <v>259.8561392940475</v>
+        <v>246.9517326366901</v>
       </c>
       <c r="D43">
-        <v>446.9343392940475</v>
+        <v>441.6001326366901</v>
       </c>
       <c r="E43">
-        <v>305.3582</v>
+        <v>312.9284000000001</v>
       </c>
       <c r="F43">
-        <v>310.3782</v>
+        <v>317.9484</v>
       </c>
       <c r="G43">
         <v>123.3</v>
@@ -4813,37 +4813,37 @@
         <v>41.4</v>
       </c>
       <c r="M43">
-        <v>45.56351976000001</v>
+        <v>46.67482512000001</v>
       </c>
       <c r="N43">
-        <v>-4.163519760000007</v>
+        <v>-5.27482512000001</v>
       </c>
       <c r="O43">
-        <v>-1.040879940000002</v>
+        <v>-1.318706280000002</v>
       </c>
       <c r="P43">
-        <v>-3.122639820000005</v>
+        <v>-3.956118840000007</v>
       </c>
       <c r="Q43">
-        <v>20.27736018</v>
+        <v>19.44388115999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09754966103133755</v>
+        <v>0.09844189656636061</v>
       </c>
       <c r="T43">
-        <v>1.008697215094193</v>
+        <v>1.026088546388921</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.2271554097338682</v>
+        <v>0.2217469475973475</v>
       </c>
       <c r="W43">
-        <v>0.1134535858510682</v>
+        <v>0.1142475480927094</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.9086216389354727</v>
+        <v>0.8869877903893899</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1050802702074271</v>
+        <v>0.1060902702074271</v>
       </c>
       <c r="C44">
-        <v>246.9517326366902</v>
+        <v>234.173152817914</v>
       </c>
       <c r="D44">
-        <v>441.6001326366901</v>
+        <v>436.391752817914</v>
       </c>
       <c r="E44">
-        <v>312.9284</v>
+        <v>320.4986</v>
       </c>
       <c r="F44">
-        <v>317.9484</v>
+        <v>325.5186</v>
       </c>
       <c r="G44">
         <v>123.3</v>
@@ -4895,37 +4895,37 @@
         <v>41.4</v>
       </c>
       <c r="M44">
-        <v>46.67482512</v>
+        <v>47.78613048</v>
       </c>
       <c r="N44">
-        <v>-5.274825120000003</v>
+        <v>-6.386130480000006</v>
       </c>
       <c r="O44">
-        <v>-1.318706280000001</v>
+        <v>-1.596532620000001</v>
       </c>
       <c r="P44">
-        <v>-3.956118840000002</v>
+        <v>-4.789597860000004</v>
       </c>
       <c r="Q44">
-        <v>19.44388116</v>
+        <v>18.61040213999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09844189656636061</v>
+        <v>0.09936543861138447</v>
       </c>
       <c r="T44">
-        <v>1.026088546388921</v>
+        <v>1.044090099834341</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.2217469475973475</v>
+        <v>0.2165900418392697</v>
       </c>
       <c r="W44">
-        <v>0.1142475480927094</v>
+        <v>0.1150045818579952</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.88698779038939</v>
+        <v>0.8663601673570787</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1060902702074271</v>
+        <v>0.1071002702074271</v>
       </c>
       <c r="C45">
-        <v>234.173152817914</v>
+        <v>221.5159996039603</v>
       </c>
       <c r="D45">
-        <v>436.391752817914</v>
+        <v>431.3047996039603</v>
       </c>
       <c r="E45">
-        <v>320.4986</v>
+        <v>328.0688</v>
       </c>
       <c r="F45">
-        <v>325.5186</v>
+        <v>333.0888</v>
       </c>
       <c r="G45">
         <v>123.3</v>
@@ -4977,37 +4977,37 @@
         <v>41.4</v>
       </c>
       <c r="M45">
-        <v>47.78613048</v>
+        <v>48.89743584</v>
       </c>
       <c r="N45">
-        <v>-6.386130480000006</v>
+        <v>-7.497435840000001</v>
       </c>
       <c r="O45">
-        <v>-1.596532620000001</v>
+        <v>-1.87435896</v>
       </c>
       <c r="P45">
-        <v>-4.789597860000004</v>
+        <v>-5.623076880000001</v>
       </c>
       <c r="Q45">
-        <v>18.61040213999999</v>
+        <v>17.77692312</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09936543861138447</v>
+        <v>0.1003219643008735</v>
       </c>
       <c r="T45">
-        <v>1.044090099834341</v>
+        <v>1.062734565902811</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2165900418392697</v>
+        <v>0.2116675408883772</v>
       </c>
       <c r="W45">
-        <v>0.1150045818579952</v>
+        <v>0.1157272049975862</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8663601673570787</v>
+        <v>0.8466701635535088</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1071002702074271</v>
+        <v>0.1081102702074271</v>
       </c>
       <c r="C46">
-        <v>221.5159996039603</v>
+        <v>208.9760755684354</v>
       </c>
       <c r="D46">
-        <v>431.3047996039603</v>
+        <v>426.3350755684354</v>
       </c>
       <c r="E46">
-        <v>328.0688</v>
+        <v>335.639</v>
       </c>
       <c r="F46">
-        <v>333.0888</v>
+        <v>340.659</v>
       </c>
       <c r="G46">
         <v>123.3</v>
@@ -5059,37 +5059,37 @@
         <v>41.4</v>
       </c>
       <c r="M46">
-        <v>48.89743584</v>
+        <v>50.0087412</v>
       </c>
       <c r="N46">
-        <v>-7.497435840000001</v>
+        <v>-8.608741200000004</v>
       </c>
       <c r="O46">
-        <v>-1.87435896</v>
+        <v>-2.152185300000001</v>
       </c>
       <c r="P46">
-        <v>-5.623076880000001</v>
+        <v>-6.456555900000003</v>
       </c>
       <c r="Q46">
-        <v>17.77692312</v>
+        <v>16.94344409999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1003219643008735</v>
+        <v>0.1013132727427075</v>
       </c>
       <c r="T46">
-        <v>1.062734565902811</v>
+        <v>1.082057012555589</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.2116675408883772</v>
+        <v>0.2069638177575243</v>
       </c>
       <c r="W46">
-        <v>0.1157272049975862</v>
+        <v>0.1164177115531954</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8466701635535088</v>
+        <v>0.8278552710300974</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1081102702074271</v>
+        <v>0.1091202702074271</v>
       </c>
       <c r="C47">
-        <v>208.9760755684354</v>
+        <v>196.5493745411359</v>
       </c>
       <c r="D47">
-        <v>426.3350755684354</v>
+        <v>421.4785745411359</v>
       </c>
       <c r="E47">
-        <v>335.639</v>
+        <v>343.2092</v>
       </c>
       <c r="F47">
-        <v>340.659</v>
+        <v>348.2292</v>
       </c>
       <c r="G47">
         <v>123.3</v>
@@ -5141,37 +5141,37 @@
         <v>41.4</v>
       </c>
       <c r="M47">
-        <v>50.0087412</v>
+        <v>51.12004656000001</v>
       </c>
       <c r="N47">
-        <v>-8.608741200000004</v>
+        <v>-9.720046560000007</v>
       </c>
       <c r="O47">
-        <v>-2.152185300000001</v>
+        <v>-2.430011640000002</v>
       </c>
       <c r="P47">
-        <v>-6.456555900000003</v>
+        <v>-7.290034920000005</v>
       </c>
       <c r="Q47">
-        <v>16.94344409999999</v>
+        <v>16.10996507999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1013132727427075</v>
+        <v>0.1023412963120169</v>
       </c>
       <c r="T47">
-        <v>1.082057012555589</v>
+        <v>1.102095105380693</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2069638177575243</v>
+        <v>0.2024646043280129</v>
       </c>
       <c r="W47">
-        <v>0.1164177115531954</v>
+        <v>0.1170781960846477</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8278552710300974</v>
+        <v>0.8098584173120518</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1091202702074271</v>
+        <v>0.1363535142049143</v>
       </c>
       <c r="C48">
-        <v>196.5493745411359</v>
+        <v>89.9414800848528</v>
       </c>
       <c r="D48">
-        <v>421.4785745411359</v>
+        <v>322.4408800848528</v>
       </c>
       <c r="E48">
-        <v>343.2092</v>
+        <v>350.7794</v>
       </c>
       <c r="F48">
-        <v>348.2292</v>
+        <v>355.7994</v>
       </c>
       <c r="G48">
         <v>123.3</v>
@@ -5223,45 +5223,45 @@
         <v>41.4</v>
       </c>
       <c r="M48">
-        <v>51.12004656000001</v>
+        <v>71.44451952</v>
       </c>
       <c r="N48">
-        <v>-9.720046560000007</v>
+        <v>-30.04451952</v>
       </c>
       <c r="O48">
-        <v>-2.430011640000002</v>
+        <v>-7.51112988</v>
       </c>
       <c r="P48">
-        <v>-7.290034920000005</v>
+        <v>-22.53338964</v>
       </c>
       <c r="Q48">
-        <v>16.10996507999999</v>
+        <v>0.8666103599999957</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1023412963120169</v>
+        <v>0.1049991396339176</v>
       </c>
       <c r="T48">
-        <v>1.102095105380693</v>
+        <v>1.15390141876571</v>
       </c>
       <c r="U48">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.2024646043280129</v>
+        <v>0.1448676549235193</v>
       </c>
       <c r="W48">
-        <v>0.1170781960846477</v>
+        <v>0.1717105748913573</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.8098584173120518</v>
+        <v>0.5794706196940773</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1363535142049143</v>
+        <v>0.1379035142049143</v>
       </c>
       <c r="C49">
-        <v>89.9414800848528</v>
+        <v>78.11590611176484</v>
       </c>
       <c r="D49">
-        <v>322.4408800848528</v>
+        <v>318.1855061117649</v>
       </c>
       <c r="E49">
-        <v>350.7794</v>
+        <v>358.3496000000001</v>
       </c>
       <c r="F49">
-        <v>355.7994</v>
+        <v>363.3696</v>
       </c>
       <c r="G49">
         <v>123.3</v>
@@ -5305,37 +5305,37 @@
         <v>41.4</v>
       </c>
       <c r="M49">
-        <v>71.44451952</v>
+        <v>72.96461568000001</v>
       </c>
       <c r="N49">
-        <v>-30.04451952</v>
+        <v>-31.56461568000001</v>
       </c>
       <c r="O49">
-        <v>-7.51112988</v>
+        <v>-7.891153920000002</v>
       </c>
       <c r="P49">
-        <v>-22.53338964</v>
+        <v>-23.67346176000001</v>
       </c>
       <c r="Q49">
-        <v>0.8666103599999957</v>
+        <v>-0.2734617600000107</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1049991396339176</v>
+        <v>0.1061375846268776</v>
       </c>
       <c r="T49">
-        <v>1.15390141876571</v>
+        <v>1.176091830665051</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1448676549235193</v>
+        <v>0.1418495787792793</v>
       </c>
       <c r="W49">
-        <v>0.1717105748913573</v>
+        <v>0.1723166045811207</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5794706196940773</v>
+        <v>0.5673983151171172</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1379035142049143</v>
+        <v>0.1394535142049143</v>
       </c>
       <c r="C50">
-        <v>78.1159061117649</v>
+        <v>66.40118867545004</v>
       </c>
       <c r="D50">
-        <v>318.1855061117649</v>
+        <v>314.04098867545</v>
       </c>
       <c r="E50">
-        <v>358.3496</v>
+        <v>365.9198</v>
       </c>
       <c r="F50">
-        <v>363.3696</v>
+        <v>370.9398</v>
       </c>
       <c r="G50">
         <v>123.3</v>
@@ -5387,37 +5387,37 @@
         <v>41.4</v>
       </c>
       <c r="M50">
-        <v>72.96461567999999</v>
+        <v>74.48471184</v>
       </c>
       <c r="N50">
-        <v>-31.56461568</v>
+        <v>-33.08471184</v>
       </c>
       <c r="O50">
-        <v>-7.891153919999999</v>
+        <v>-8.271177960000001</v>
       </c>
       <c r="P50">
-        <v>-23.67346176</v>
+        <v>-24.81353388</v>
       </c>
       <c r="Q50">
-        <v>-0.2734617599999964</v>
+        <v>-1.413533880000003</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1061375846268776</v>
+        <v>0.1073206745215222</v>
       </c>
       <c r="T50">
-        <v>1.176091830665051</v>
+        <v>1.199152454795738</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1418495787792793</v>
+        <v>0.1389546894164369</v>
       </c>
       <c r="W50">
-        <v>0.1723166045811207</v>
+        <v>0.1728978983651795</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5673983151171174</v>
+        <v>0.5558187576657476</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1394535142049143</v>
+        <v>0.1410035142049143</v>
       </c>
       <c r="C51">
-        <v>66.40118867545004</v>
+        <v>54.79305159792938</v>
       </c>
       <c r="D51">
-        <v>314.04098867545</v>
+        <v>310.0030515979294</v>
       </c>
       <c r="E51">
-        <v>365.9198</v>
+        <v>373.49</v>
       </c>
       <c r="F51">
-        <v>370.9398</v>
+        <v>378.51</v>
       </c>
       <c r="G51">
         <v>123.3</v>
@@ -5469,37 +5469,37 @@
         <v>41.4</v>
       </c>
       <c r="M51">
-        <v>74.48471184</v>
+        <v>76.004808</v>
       </c>
       <c r="N51">
-        <v>-33.08471184</v>
+        <v>-34.604808</v>
       </c>
       <c r="O51">
-        <v>-8.271177960000001</v>
+        <v>-8.651202</v>
       </c>
       <c r="P51">
-        <v>-24.81353388</v>
+        <v>-25.953606</v>
       </c>
       <c r="Q51">
-        <v>-1.413533880000003</v>
+        <v>-2.553606000000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1073206745215222</v>
+        <v>0.1085510880119527</v>
       </c>
       <c r="T51">
-        <v>1.199152454795738</v>
+        <v>1.223135503891653</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1389546894164369</v>
+        <v>0.1361755956281082</v>
       </c>
       <c r="W51">
-        <v>0.1728978983651795</v>
+        <v>0.1734559403978759</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5558187576657476</v>
+        <v>0.5447023825124326</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1410035142049143</v>
+        <v>0.1425535142049143</v>
       </c>
       <c r="C52">
-        <v>54.79305159792938</v>
+        <v>43.28743584151425</v>
       </c>
       <c r="D52">
-        <v>310.0030515979294</v>
+        <v>306.0676358415142</v>
       </c>
       <c r="E52">
-        <v>373.49</v>
+        <v>381.0602</v>
       </c>
       <c r="F52">
-        <v>378.51</v>
+        <v>386.0802</v>
       </c>
       <c r="G52">
         <v>123.3</v>
@@ -5551,37 +5551,37 @@
         <v>41.4</v>
       </c>
       <c r="M52">
-        <v>76.004808</v>
+        <v>77.52490416000001</v>
       </c>
       <c r="N52">
-        <v>-34.604808</v>
+        <v>-36.12490416000001</v>
       </c>
       <c r="O52">
-        <v>-8.651202</v>
+        <v>-9.031226040000002</v>
       </c>
       <c r="P52">
-        <v>-25.953606</v>
+        <v>-27.09367812000001</v>
       </c>
       <c r="Q52">
-        <v>-2.553606000000002</v>
+        <v>-3.693678120000008</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1085510880119527</v>
+        <v>0.1098317224611762</v>
       </c>
       <c r="T52">
-        <v>1.223135503891653</v>
+        <v>1.248097452950666</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1361755956281082</v>
+        <v>0.1335054859099099</v>
       </c>
       <c r="W52">
-        <v>0.1734559403978759</v>
+        <v>0.1739920984292901</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5447023825124326</v>
+        <v>0.5340219436396398</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1425535142049143</v>
+        <v>0.1441035142049143</v>
       </c>
       <c r="C53">
-        <v>43.28743584151425</v>
+        <v>31.88048589885784</v>
       </c>
       <c r="D53">
-        <v>306.0676358415142</v>
+        <v>302.2308858988578</v>
       </c>
       <c r="E53">
-        <v>381.0602</v>
+        <v>388.6304</v>
       </c>
       <c r="F53">
-        <v>386.0802</v>
+        <v>393.6504</v>
       </c>
       <c r="G53">
         <v>123.3</v>
@@ -5633,37 +5633,37 @@
         <v>41.4</v>
       </c>
       <c r="M53">
-        <v>77.52490416000001</v>
+        <v>79.04500032</v>
       </c>
       <c r="N53">
-        <v>-36.12490416000001</v>
+        <v>-37.64500032</v>
       </c>
       <c r="O53">
-        <v>-9.031226040000002</v>
+        <v>-9.41125008</v>
       </c>
       <c r="P53">
-        <v>-27.09367812000001</v>
+        <v>-28.23375024</v>
       </c>
       <c r="Q53">
-        <v>-3.693678120000008</v>
+        <v>-4.833750240000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1098317224611762</v>
+        <v>0.1111657166791174</v>
       </c>
       <c r="T53">
-        <v>1.248097452950666</v>
+        <v>1.274099483220472</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1335054859099099</v>
+        <v>0.1309380727193348</v>
       </c>
       <c r="W53">
-        <v>0.1739920984292901</v>
+        <v>0.1745076349979576</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5340219436396398</v>
+        <v>0.5237522908773391</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1441035142049143</v>
+        <v>0.1456535142049143</v>
       </c>
       <c r="C54">
-        <v>31.88048589885784</v>
+        <v>20.56853719398788</v>
       </c>
       <c r="D54">
-        <v>302.2308858988578</v>
+        <v>298.4891371939879</v>
       </c>
       <c r="E54">
-        <v>388.6304</v>
+        <v>396.2006</v>
       </c>
       <c r="F54">
-        <v>393.6504</v>
+        <v>401.2206</v>
       </c>
       <c r="G54">
         <v>123.3</v>
@@ -5715,37 +5715,37 @@
         <v>41.4</v>
       </c>
       <c r="M54">
-        <v>79.04500032</v>
+        <v>80.56509647999999</v>
       </c>
       <c r="N54">
-        <v>-37.64500032</v>
+        <v>-39.16509648</v>
       </c>
       <c r="O54">
-        <v>-9.41125008</v>
+        <v>-9.791274119999999</v>
       </c>
       <c r="P54">
-        <v>-28.23375024</v>
+        <v>-29.37382236</v>
       </c>
       <c r="Q54">
-        <v>-4.833750240000001</v>
+        <v>-5.97382236</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1111657166791174</v>
+        <v>0.1125564766084603</v>
       </c>
       <c r="T54">
-        <v>1.274099483220472</v>
+        <v>1.301207982863461</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1309380727193348</v>
+        <v>0.1284675430453851</v>
       </c>
       <c r="W54">
-        <v>0.1745076349979576</v>
+        <v>0.1750037173564867</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5237522908773391</v>
+        <v>0.5138701721815402</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1456535142049143</v>
+        <v>0.1472035142049143</v>
       </c>
       <c r="C55">
-        <v>20.56853719398788</v>
+        <v>9.348104407778635</v>
       </c>
       <c r="D55">
-        <v>298.4891371939879</v>
+        <v>294.8389044077786</v>
       </c>
       <c r="E55">
-        <v>396.2006</v>
+        <v>403.7708</v>
       </c>
       <c r="F55">
-        <v>401.2206</v>
+        <v>408.7908</v>
       </c>
       <c r="G55">
         <v>123.3</v>
@@ -5797,37 +5797,37 @@
         <v>41.4</v>
       </c>
       <c r="M55">
-        <v>80.56509647999999</v>
+        <v>82.08519264</v>
       </c>
       <c r="N55">
-        <v>-39.16509648</v>
+        <v>-40.68519264</v>
       </c>
       <c r="O55">
-        <v>-9.791274119999999</v>
+        <v>-10.17129816</v>
       </c>
       <c r="P55">
-        <v>-29.37382236</v>
+        <v>-30.51389448</v>
       </c>
       <c r="Q55">
-        <v>-5.97382236</v>
+        <v>-7.113894480000006</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1125564766084603</v>
+        <v>0.1140077043608181</v>
       </c>
       <c r="T55">
-        <v>1.301207982863461</v>
+        <v>1.32949511292571</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1284675430453851</v>
+        <v>0.1260885144704705</v>
       </c>
       <c r="W55">
-        <v>0.1750037173564867</v>
+        <v>0.1754814262943295</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5138701721815402</v>
+        <v>0.504354057881882</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1472035142049143</v>
+        <v>0.1683437733431584</v>
       </c>
       <c r="C56">
-        <v>9.348104407778635</v>
+        <v>-40.36870472864751</v>
       </c>
       <c r="D56">
-        <v>294.8389044077786</v>
+        <v>252.6922952713525</v>
       </c>
       <c r="E56">
-        <v>403.7708</v>
+        <v>411.3410000000001</v>
       </c>
       <c r="F56">
-        <v>408.7908</v>
+        <v>416.361</v>
       </c>
       <c r="G56">
         <v>123.3</v>
@@ -5879,45 +5879,45 @@
         <v>41.4</v>
       </c>
       <c r="M56">
-        <v>82.08519264</v>
+        <v>98.17792380000002</v>
       </c>
       <c r="N56">
-        <v>-40.68519264</v>
+        <v>-56.77792380000002</v>
       </c>
       <c r="O56">
-        <v>-10.17129816</v>
+        <v>-14.19448095</v>
       </c>
       <c r="P56">
-        <v>-30.51389448</v>
+        <v>-42.58344285000001</v>
       </c>
       <c r="Q56">
-        <v>-7.113894480000006</v>
+        <v>-19.18344285000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1140077043608181</v>
+        <v>0.116279562542712</v>
       </c>
       <c r="T56">
-        <v>1.32949511292571</v>
+        <v>1.373777857498231</v>
       </c>
       <c r="U56">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1260885144704705</v>
+        <v>0.1054208481846099</v>
       </c>
       <c r="W56">
-        <v>0.1754814262943295</v>
+        <v>0.210941763998069</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.504354057881882</v>
+        <v>0.4216833927384396</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1683437733431584</v>
+        <v>0.1702437733431583</v>
       </c>
       <c r="C57">
-        <v>-40.36870472864751</v>
+        <v>-51.14420745592724</v>
       </c>
       <c r="D57">
-        <v>252.6922952713525</v>
+        <v>249.4869925440728</v>
       </c>
       <c r="E57">
-        <v>411.3410000000001</v>
+        <v>418.9112000000001</v>
       </c>
       <c r="F57">
-        <v>416.361</v>
+        <v>423.9312</v>
       </c>
       <c r="G57">
         <v>123.3</v>
@@ -5961,37 +5961,37 @@
         <v>41.4</v>
       </c>
       <c r="M57">
-        <v>98.17792380000002</v>
+        <v>99.96297696000002</v>
       </c>
       <c r="N57">
-        <v>-56.77792380000002</v>
+        <v>-58.56297696000002</v>
       </c>
       <c r="O57">
-        <v>-14.19448095</v>
+        <v>-14.64074424000001</v>
       </c>
       <c r="P57">
-        <v>-42.58344285000001</v>
+        <v>-43.92223272000002</v>
       </c>
       <c r="Q57">
-        <v>-19.18344285000001</v>
+        <v>-20.52223272000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.116279562542712</v>
+        <v>0.1178813707823191</v>
       </c>
       <c r="T57">
-        <v>1.373777857498231</v>
+        <v>1.405000081532282</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1054208481846099</v>
+        <v>0.1035383330384561</v>
       </c>
       <c r="W57">
-        <v>0.210941763998069</v>
+        <v>0.211385661069532</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4216833927384396</v>
+        <v>0.4141533321538245</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1702437733431583</v>
+        <v>0.1721437733431583</v>
       </c>
       <c r="C58">
-        <v>-51.14420745592724</v>
+        <v>-61.8394127075461</v>
       </c>
       <c r="D58">
-        <v>249.4869925440728</v>
+        <v>246.361987292454</v>
       </c>
       <c r="E58">
-        <v>418.9112000000001</v>
+        <v>426.4814000000001</v>
       </c>
       <c r="F58">
-        <v>423.9312</v>
+        <v>431.5014</v>
       </c>
       <c r="G58">
         <v>123.3</v>
@@ -6043,37 +6043,37 @@
         <v>41.4</v>
       </c>
       <c r="M58">
-        <v>99.96297696000002</v>
+        <v>101.74803012</v>
       </c>
       <c r="N58">
-        <v>-58.56297696000002</v>
+        <v>-60.34803012000001</v>
       </c>
       <c r="O58">
-        <v>-14.64074424000001</v>
+        <v>-15.08700753</v>
       </c>
       <c r="P58">
-        <v>-43.92223272000002</v>
+        <v>-45.26102259000001</v>
       </c>
       <c r="Q58">
-        <v>-20.52223272000002</v>
+        <v>-21.86102259000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1178813707823191</v>
+        <v>0.1195576817307451</v>
       </c>
       <c r="T58">
-        <v>1.405000081532282</v>
+        <v>1.437674502033033</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1035383330384561</v>
+        <v>0.1017218710553253</v>
       </c>
       <c r="W58">
-        <v>0.211385661069532</v>
+        <v>0.2118139828051543</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4141533321538245</v>
+        <v>0.4068874842213014</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1721437733431583</v>
+        <v>0.1740437733431583</v>
       </c>
       <c r="C59">
-        <v>-61.8394127075461</v>
+        <v>-72.45730050862522</v>
       </c>
       <c r="D59">
-        <v>246.361987292454</v>
+        <v>243.3142994913748</v>
       </c>
       <c r="E59">
-        <v>426.4814000000001</v>
+        <v>434.0516000000001</v>
       </c>
       <c r="F59">
-        <v>431.5014</v>
+        <v>439.0716</v>
       </c>
       <c r="G59">
         <v>123.3</v>
@@ -6125,37 +6125,37 @@
         <v>41.4</v>
       </c>
       <c r="M59">
-        <v>101.74803012</v>
+        <v>103.53308328</v>
       </c>
       <c r="N59">
-        <v>-60.34803012000001</v>
+        <v>-62.13308328000002</v>
       </c>
       <c r="O59">
-        <v>-15.08700753</v>
+        <v>-15.53327082</v>
       </c>
       <c r="P59">
-        <v>-45.26102259000001</v>
+        <v>-46.59981246000001</v>
       </c>
       <c r="Q59">
-        <v>-21.86102259000001</v>
+        <v>-23.19981246000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1195576817307451</v>
+        <v>0.1213138170100486</v>
       </c>
       <c r="T59">
-        <v>1.437674502033033</v>
+        <v>1.471904847319534</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1017218710553253</v>
+        <v>0.09996804569230248</v>
       </c>
       <c r="W59">
-        <v>0.2118139828051543</v>
+        <v>0.2122275348257551</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4068874842213014</v>
+        <v>0.3998721827692099</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1740437733431583</v>
+        <v>0.1759437733431583</v>
       </c>
       <c r="C60">
-        <v>-72.45730050862511</v>
+        <v>-83.00070522536237</v>
       </c>
       <c r="D60">
-        <v>243.3142994913748</v>
+        <v>240.3410947746376</v>
       </c>
       <c r="E60">
-        <v>434.0516</v>
+        <v>441.6218</v>
       </c>
       <c r="F60">
-        <v>439.0715999999999</v>
+        <v>446.6418</v>
       </c>
       <c r="G60">
         <v>123.3</v>
@@ -6207,37 +6207,37 @@
         <v>41.4</v>
       </c>
       <c r="M60">
-        <v>103.53308328</v>
+        <v>105.31813644</v>
       </c>
       <c r="N60">
-        <v>-62.13308327999999</v>
+        <v>-63.91813644</v>
       </c>
       <c r="O60">
-        <v>-15.53327082</v>
+        <v>-15.97953411</v>
       </c>
       <c r="P60">
-        <v>-46.59981245999999</v>
+        <v>-47.93860233</v>
       </c>
       <c r="Q60">
-        <v>-23.19981245999999</v>
+        <v>-24.53860233</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1213138170100485</v>
+        <v>0.1231556174249278</v>
       </c>
       <c r="T60">
-        <v>1.471904847319533</v>
+        <v>1.507804965546838</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.09996804569230251</v>
+        <v>0.09827367203650075</v>
       </c>
       <c r="W60">
-        <v>0.2122275348257551</v>
+        <v>0.2126270681337931</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.39987218276921</v>
+        <v>0.393094688146003</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1759437733431583</v>
+        <v>0.1778437733431583</v>
       </c>
       <c r="C61">
-        <v>-83.00070522536237</v>
+        <v>-93.472324357069</v>
       </c>
       <c r="D61">
-        <v>240.3410947746376</v>
+        <v>237.439675642931</v>
       </c>
       <c r="E61">
-        <v>441.6218</v>
+        <v>449.192</v>
       </c>
       <c r="F61">
-        <v>446.6418</v>
+        <v>454.212</v>
       </c>
       <c r="G61">
         <v>123.3</v>
@@ -6289,37 +6289,37 @@
         <v>41.4</v>
       </c>
       <c r="M61">
-        <v>105.31813644</v>
+        <v>107.1031896</v>
       </c>
       <c r="N61">
-        <v>-63.91813644</v>
+        <v>-65.7031896</v>
       </c>
       <c r="O61">
-        <v>-15.97953411</v>
+        <v>-16.4257974</v>
       </c>
       <c r="P61">
-        <v>-47.93860233</v>
+        <v>-49.2773922</v>
       </c>
       <c r="Q61">
-        <v>-24.53860233</v>
+        <v>-25.8773922</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1231556174249278</v>
+        <v>0.125089507860551</v>
       </c>
       <c r="T61">
-        <v>1.507804965546838</v>
+        <v>1.54550008968551</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.09827367203650075</v>
+        <v>0.09663577750255907</v>
       </c>
       <c r="W61">
-        <v>0.2126270681337931</v>
+        <v>0.2130132836648966</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.393094688146003</v>
+        <v>0.3865431100102363</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1778437733431583</v>
+        <v>0.1797437733431583</v>
       </c>
       <c r="C62">
-        <v>-93.472324357069</v>
+        <v>-103.8747266989751</v>
       </c>
       <c r="D62">
-        <v>237.439675642931</v>
+        <v>234.6074733010249</v>
       </c>
       <c r="E62">
-        <v>449.192</v>
+        <v>456.7622</v>
       </c>
       <c r="F62">
-        <v>454.212</v>
+        <v>461.7822</v>
       </c>
       <c r="G62">
         <v>123.3</v>
@@ -6371,37 +6371,37 @@
         <v>41.4</v>
       </c>
       <c r="M62">
-        <v>107.1031896</v>
+        <v>108.88824276</v>
       </c>
       <c r="N62">
-        <v>-65.7031896</v>
+        <v>-67.48824275999999</v>
       </c>
       <c r="O62">
-        <v>-16.4257974</v>
+        <v>-16.87206069</v>
       </c>
       <c r="P62">
-        <v>-49.2773922</v>
+        <v>-50.61618206999999</v>
       </c>
       <c r="Q62">
-        <v>-25.8773922</v>
+        <v>-27.21618207</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.125089507860551</v>
+        <v>0.1271225721646677</v>
       </c>
       <c r="T62">
-        <v>1.54550008968551</v>
+        <v>1.585128297113343</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.09663577750255907</v>
+        <v>0.09505158442874664</v>
       </c>
       <c r="W62">
-        <v>0.2130132836648966</v>
+        <v>0.2133868363917016</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3865431100102363</v>
+        <v>0.3802063377149866</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1797437733431583</v>
+        <v>0.1816437733431583</v>
       </c>
       <c r="C63">
-        <v>-103.8747266989751</v>
+        <v>-114.2103599277183</v>
       </c>
       <c r="D63">
-        <v>234.6074733010249</v>
+        <v>231.8420400722816</v>
       </c>
       <c r="E63">
-        <v>456.7622</v>
+        <v>464.3324</v>
       </c>
       <c r="F63">
-        <v>461.7822</v>
+        <v>469.3524</v>
       </c>
       <c r="G63">
         <v>123.3</v>
@@ -6453,37 +6453,37 @@
         <v>41.4</v>
       </c>
       <c r="M63">
-        <v>108.88824276</v>
+        <v>110.67329592</v>
       </c>
       <c r="N63">
-        <v>-67.48824275999999</v>
+        <v>-69.27329592000001</v>
       </c>
       <c r="O63">
-        <v>-16.87206069</v>
+        <v>-17.31832398</v>
       </c>
       <c r="P63">
-        <v>-50.61618206999999</v>
+        <v>-51.95497194000001</v>
       </c>
       <c r="Q63">
-        <v>-27.21618207</v>
+        <v>-28.55497194000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1271225721646677</v>
+        <v>0.1292626398532115</v>
       </c>
       <c r="T63">
-        <v>1.585128297113343</v>
+        <v>1.626842199668957</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09505158442874664</v>
+        <v>0.09351849435731524</v>
       </c>
       <c r="W63">
-        <v>0.2133868363917016</v>
+        <v>0.213748339030545</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3802063377149866</v>
+        <v>0.3740739774292609</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1816437733431583</v>
+        <v>0.1835437733431583</v>
       </c>
       <c r="C64">
-        <v>-114.2103599277183</v>
+        <v>-124.4815576566024</v>
       </c>
       <c r="D64">
-        <v>231.8420400722816</v>
+        <v>229.1410423433976</v>
       </c>
       <c r="E64">
-        <v>464.3324</v>
+        <v>471.9026</v>
       </c>
       <c r="F64">
-        <v>469.3524</v>
+        <v>476.9226</v>
       </c>
       <c r="G64">
         <v>123.3</v>
@@ -6535,37 +6535,37 @@
         <v>41.4</v>
       </c>
       <c r="M64">
-        <v>110.67329592</v>
+        <v>112.45834908</v>
       </c>
       <c r="N64">
-        <v>-69.27329592000001</v>
+        <v>-71.05834908</v>
       </c>
       <c r="O64">
-        <v>-17.31832398</v>
+        <v>-17.76458727</v>
       </c>
       <c r="P64">
-        <v>-51.95497194000001</v>
+        <v>-53.29376181</v>
       </c>
       <c r="Q64">
-        <v>-28.55497194000001</v>
+        <v>-29.89376181</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1292626398532115</v>
+        <v>0.1315183868762713</v>
       </c>
       <c r="T64">
-        <v>1.626842199668957</v>
+        <v>1.670810907768119</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.09351849435731524</v>
+        <v>0.09203407381196102</v>
       </c>
       <c r="W64">
-        <v>0.213748339030545</v>
+        <v>0.2140983653951396</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3740739774292609</v>
+        <v>0.3681362952478442</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1835437733431583</v>
+        <v>0.1854437733431584</v>
       </c>
       <c r="C65">
-        <v>-124.4815576566024</v>
+        <v>-134.6905460033634</v>
       </c>
       <c r="D65">
-        <v>229.1410423433976</v>
+        <v>226.5022539966366</v>
       </c>
       <c r="E65">
-        <v>471.9026</v>
+        <v>479.4728</v>
       </c>
       <c r="F65">
-        <v>476.9226</v>
+        <v>484.4928</v>
       </c>
       <c r="G65">
         <v>123.3</v>
@@ -6617,37 +6617,37 @@
         <v>41.4</v>
       </c>
       <c r="M65">
-        <v>112.45834908</v>
+        <v>114.24340224</v>
       </c>
       <c r="N65">
-        <v>-71.05834908</v>
+        <v>-72.84340224000002</v>
       </c>
       <c r="O65">
-        <v>-17.76458727</v>
+        <v>-18.21085056</v>
       </c>
       <c r="P65">
-        <v>-53.29376181</v>
+        <v>-54.63255168000001</v>
       </c>
       <c r="Q65">
-        <v>-29.89376181</v>
+        <v>-31.23255168000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1315183868762713</v>
+        <v>0.13389945317839</v>
       </c>
       <c r="T65">
-        <v>1.670810907768119</v>
+        <v>1.717222321872789</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09203407381196102</v>
+        <v>0.09059604140864913</v>
       </c>
       <c r="W65">
-        <v>0.2140983653951396</v>
+        <v>0.2144374534358406</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3681362952478442</v>
+        <v>0.3623841656345964</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1854437733431584</v>
+        <v>0.1873437733431583</v>
       </c>
       <c r="C66">
-        <v>-134.6905460033634</v>
+        <v>-144.8394497092972</v>
       </c>
       <c r="D66">
-        <v>226.5022539966366</v>
+        <v>223.9235502907028</v>
       </c>
       <c r="E66">
-        <v>479.4728</v>
+        <v>487.043</v>
       </c>
       <c r="F66">
-        <v>484.4928</v>
+        <v>492.063</v>
       </c>
       <c r="G66">
         <v>123.3</v>
@@ -6699,37 +6699,37 @@
         <v>41.4</v>
       </c>
       <c r="M66">
-        <v>114.24340224</v>
+        <v>116.0284554</v>
       </c>
       <c r="N66">
-        <v>-72.84340224000002</v>
+        <v>-74.62845540000001</v>
       </c>
       <c r="O66">
-        <v>-18.21085056</v>
+        <v>-18.65711385</v>
       </c>
       <c r="P66">
-        <v>-54.63255168000001</v>
+        <v>-55.97134155000001</v>
       </c>
       <c r="Q66">
-        <v>-31.23255168000001</v>
+        <v>-32.57134155000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.13389945317839</v>
+        <v>0.1364165804120583</v>
       </c>
       <c r="T66">
-        <v>1.717222321872789</v>
+        <v>1.76628581678344</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09059604140864913</v>
+        <v>0.08920225615620839</v>
       </c>
       <c r="W66">
-        <v>0.2144374534358406</v>
+        <v>0.2147661079983661</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3623841656345964</v>
+        <v>0.3568090246248334</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1873437733431583</v>
+        <v>0.1892437733431583</v>
       </c>
       <c r="C67">
-        <v>-144.8394497092972</v>
+        <v>-154.9302978450982</v>
       </c>
       <c r="D67">
-        <v>223.9235502907028</v>
+        <v>221.4029021549018</v>
       </c>
       <c r="E67">
-        <v>487.043</v>
+        <v>494.6132</v>
       </c>
       <c r="F67">
-        <v>492.063</v>
+        <v>499.6332</v>
       </c>
       <c r="G67">
         <v>123.3</v>
@@ -6781,37 +6781,37 @@
         <v>41.4</v>
       </c>
       <c r="M67">
-        <v>116.0284554</v>
+        <v>117.81350856</v>
       </c>
       <c r="N67">
-        <v>-74.62845540000001</v>
+        <v>-76.41350856</v>
       </c>
       <c r="O67">
-        <v>-18.65711385</v>
+        <v>-19.10337714</v>
       </c>
       <c r="P67">
-        <v>-55.97134155000001</v>
+        <v>-57.31013142</v>
       </c>
       <c r="Q67">
-        <v>-32.57134155000001</v>
+        <v>-33.91013142</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1364165804120583</v>
+        <v>0.1390817739535894</v>
       </c>
       <c r="T67">
-        <v>1.76628581678344</v>
+        <v>1.818235399630012</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08920225615620839</v>
+        <v>0.08785070682050826</v>
       </c>
       <c r="W67">
-        <v>0.2147661079983661</v>
+        <v>0.2150848033317242</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3568090246248334</v>
+        <v>0.3514028272820331</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1892437733431583</v>
+        <v>0.1911437733431584</v>
       </c>
       <c r="C68">
-        <v>-154.9302978450982</v>
+        <v>-164.9650291356132</v>
       </c>
       <c r="D68">
-        <v>221.4029021549018</v>
+        <v>218.9383708643869</v>
       </c>
       <c r="E68">
-        <v>494.6132</v>
+        <v>502.1834000000001</v>
       </c>
       <c r="F68">
-        <v>499.6332</v>
+        <v>507.2034</v>
       </c>
       <c r="G68">
         <v>123.3</v>
@@ -6863,37 +6863,37 @@
         <v>41.4</v>
       </c>
       <c r="M68">
-        <v>117.81350856</v>
+        <v>119.59856172</v>
       </c>
       <c r="N68">
-        <v>-76.41350856</v>
+        <v>-78.19856172000001</v>
       </c>
       <c r="O68">
-        <v>-19.10337714</v>
+        <v>-19.54964043</v>
       </c>
       <c r="P68">
-        <v>-57.31013142</v>
+        <v>-58.64892129000001</v>
       </c>
       <c r="Q68">
-        <v>-33.91013142</v>
+        <v>-35.24892129000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1390817739535894</v>
+        <v>0.1419084943764254</v>
       </c>
       <c r="T68">
-        <v>1.818235399630012</v>
+        <v>1.873333442043043</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08785070682050826</v>
+        <v>0.08653950224109767</v>
       </c>
       <c r="W68">
-        <v>0.2150848033317242</v>
+        <v>0.2153939853715492</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3514028272820331</v>
+        <v>0.3461580089643908</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1911437733431584</v>
+        <v>0.1930437733431583</v>
       </c>
       <c r="C69">
-        <v>-164.9650291356132</v>
+        <v>-174.9454969328772</v>
       </c>
       <c r="D69">
-        <v>218.9383708643869</v>
+        <v>216.5281030671228</v>
       </c>
       <c r="E69">
-        <v>502.1834000000001</v>
+        <v>509.7536</v>
       </c>
       <c r="F69">
-        <v>507.2034</v>
+        <v>514.7736</v>
       </c>
       <c r="G69">
         <v>123.3</v>
@@ -6945,37 +6945,37 @@
         <v>41.4</v>
       </c>
       <c r="M69">
-        <v>119.59856172</v>
+        <v>121.38361488</v>
       </c>
       <c r="N69">
-        <v>-78.19856172000001</v>
+        <v>-79.98361488</v>
       </c>
       <c r="O69">
-        <v>-19.54964043</v>
+        <v>-19.99590372</v>
       </c>
       <c r="P69">
-        <v>-58.64892129000001</v>
+        <v>-59.98771116</v>
       </c>
       <c r="Q69">
-        <v>-35.24892129000001</v>
+        <v>-36.58771116</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1419084943764254</v>
+        <v>0.1449118848256887</v>
       </c>
       <c r="T69">
-        <v>1.873333442043043</v>
+        <v>1.931875112106887</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08653950224109767</v>
+        <v>0.08526686250225801</v>
       </c>
       <c r="W69">
-        <v>0.2153939853715492</v>
+        <v>0.2156940738219676</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3461580089643908</v>
+        <v>0.341067450009032</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1930437733431583</v>
+        <v>0.1949437733431583</v>
       </c>
       <c r="C70">
-        <v>-174.9454969328772</v>
+        <v>-184.8734738642416</v>
       </c>
       <c r="D70">
-        <v>216.5281030671228</v>
+        <v>214.1703261357583</v>
       </c>
       <c r="E70">
-        <v>509.7536</v>
+        <v>517.3238</v>
       </c>
       <c r="F70">
-        <v>514.7736</v>
+        <v>522.3438</v>
       </c>
       <c r="G70">
         <v>123.3</v>
@@ -7027,37 +7027,37 @@
         <v>41.4</v>
       </c>
       <c r="M70">
-        <v>121.38361488</v>
+        <v>123.16866804</v>
       </c>
       <c r="N70">
-        <v>-79.98361488</v>
+        <v>-81.76866803999999</v>
       </c>
       <c r="O70">
-        <v>-19.99590372</v>
+        <v>-20.44216701</v>
       </c>
       <c r="P70">
-        <v>-59.98771116</v>
+        <v>-61.32650103</v>
       </c>
       <c r="Q70">
-        <v>-36.58771116</v>
+        <v>-37.92650103</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1449118848256887</v>
+        <v>0.1481090424007109</v>
       </c>
       <c r="T70">
-        <v>1.931875112106887</v>
+        <v>1.994193664110335</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08526686250225801</v>
+        <v>0.08403111087179051</v>
       </c>
       <c r="W70">
-        <v>0.2156940738219676</v>
+        <v>0.2159854640564318</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.341067450009032</v>
+        <v>0.3361244434871621</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1949437733431583</v>
+        <v>0.1968437733431583</v>
       </c>
       <c r="C71">
-        <v>-184.8734738642416</v>
+        <v>-194.7506561800911</v>
       </c>
       <c r="D71">
-        <v>214.1703261357583</v>
+        <v>211.8633438199088</v>
       </c>
       <c r="E71">
-        <v>517.3238</v>
+        <v>524.894</v>
       </c>
       <c r="F71">
-        <v>522.3438</v>
+        <v>529.914</v>
       </c>
       <c r="G71">
         <v>123.3</v>
@@ -7109,37 +7109,37 @@
         <v>41.4</v>
       </c>
       <c r="M71">
-        <v>123.16866804</v>
+        <v>124.9537212</v>
       </c>
       <c r="N71">
-        <v>-81.76866803999999</v>
+        <v>-83.55372120000001</v>
       </c>
       <c r="O71">
-        <v>-20.44216701</v>
+        <v>-20.8884303</v>
       </c>
       <c r="P71">
-        <v>-61.32650103</v>
+        <v>-62.66529090000001</v>
       </c>
       <c r="Q71">
-        <v>-37.92650103</v>
+        <v>-39.26529090000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1481090424007109</v>
+        <v>0.151519343814068</v>
       </c>
       <c r="T71">
-        <v>1.994193664110335</v>
+        <v>2.060666786247347</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08403111087179051</v>
+        <v>0.08283066643076492</v>
       </c>
       <c r="W71">
-        <v>0.2159854640564318</v>
+        <v>0.2162685288556256</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3361244434871621</v>
+        <v>0.3313226657230597</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1968437733431583</v>
+        <v>0.1987437733431583</v>
       </c>
       <c r="C72">
-        <v>-194.7506561800911</v>
+        <v>-204.5786678235622</v>
       </c>
       <c r="D72">
-        <v>211.8633438199088</v>
+        <v>209.6055321764379</v>
       </c>
       <c r="E72">
-        <v>524.894</v>
+        <v>532.4642000000001</v>
       </c>
       <c r="F72">
-        <v>529.914</v>
+        <v>537.4842000000001</v>
       </c>
       <c r="G72">
         <v>123.3</v>
@@ -7191,37 +7191,37 @@
         <v>41.4</v>
       </c>
       <c r="M72">
-        <v>124.9537212</v>
+        <v>126.73877436</v>
       </c>
       <c r="N72">
-        <v>-83.55372120000001</v>
+        <v>-85.33877436000003</v>
       </c>
       <c r="O72">
-        <v>-20.8884303</v>
+        <v>-21.33469359000001</v>
       </c>
       <c r="P72">
-        <v>-62.66529090000001</v>
+        <v>-64.00408077000003</v>
       </c>
       <c r="Q72">
-        <v>-39.26529090000001</v>
+        <v>-40.60408077000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.151519343814068</v>
+        <v>0.1551648384283462</v>
       </c>
       <c r="T72">
-        <v>2.060666786247347</v>
+        <v>2.131724261635187</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08283066643076492</v>
+        <v>0.08166403732610625</v>
       </c>
       <c r="W72">
-        <v>0.2162685288556256</v>
+        <v>0.2165436199985042</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3313226657230597</v>
+        <v>0.326656149304425</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1987437733431583</v>
+        <v>0.2006437733431583</v>
       </c>
       <c r="C73">
-        <v>-204.5786678235621</v>
+        <v>-214.3590642427796</v>
       </c>
       <c r="D73">
-        <v>209.6055321764379</v>
+        <v>207.3953357572204</v>
       </c>
       <c r="E73">
-        <v>532.4642</v>
+        <v>540.0344</v>
       </c>
       <c r="F73">
-        <v>537.4842</v>
+        <v>545.0544</v>
       </c>
       <c r="G73">
         <v>123.3</v>
@@ -7273,37 +7273,37 @@
         <v>41.4</v>
       </c>
       <c r="M73">
-        <v>126.73877436</v>
+        <v>128.52382752</v>
       </c>
       <c r="N73">
-        <v>-85.33877436</v>
+        <v>-87.12382751999999</v>
       </c>
       <c r="O73">
-        <v>-21.33469359</v>
+        <v>-21.78095688</v>
       </c>
       <c r="P73">
-        <v>-64.00408077</v>
+        <v>-65.34287064</v>
       </c>
       <c r="Q73">
-        <v>-40.60408077</v>
+        <v>-41.94287064</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1551648384283461</v>
+        <v>0.1590707255150728</v>
       </c>
       <c r="T73">
-        <v>2.131724261635186</v>
+        <v>2.207857270979299</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08166403732610626</v>
+        <v>0.0805298145854659</v>
       </c>
       <c r="W73">
-        <v>0.2165436199985042</v>
+        <v>0.2168110697207472</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3266561493044251</v>
+        <v>0.3221192583418636</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2006437733431583</v>
+        <v>0.2025437733431583</v>
       </c>
       <c r="C74">
-        <v>-214.3590642427796</v>
+        <v>-224.0933359644225</v>
       </c>
       <c r="D74">
-        <v>207.3953357572204</v>
+        <v>205.2312640355775</v>
       </c>
       <c r="E74">
-        <v>540.0344</v>
+        <v>547.6046</v>
       </c>
       <c r="F74">
-        <v>545.0544</v>
+        <v>552.6246</v>
       </c>
       <c r="G74">
         <v>123.3</v>
@@ -7355,37 +7355,37 @@
         <v>41.4</v>
       </c>
       <c r="M74">
-        <v>128.52382752</v>
+        <v>130.30888068</v>
       </c>
       <c r="N74">
-        <v>-87.12382751999999</v>
+        <v>-88.90888068000001</v>
       </c>
       <c r="O74">
-        <v>-21.78095688</v>
+        <v>-22.22722017</v>
       </c>
       <c r="P74">
-        <v>-65.34287064</v>
+        <v>-66.68166051</v>
       </c>
       <c r="Q74">
-        <v>-41.94287064</v>
+        <v>-43.28166051</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1590707255150728</v>
+        <v>0.1632659375711866</v>
       </c>
       <c r="T74">
-        <v>2.207857270979299</v>
+        <v>2.289629762497051</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0805298145854659</v>
+        <v>0.07942666644045951</v>
       </c>
       <c r="W74">
-        <v>0.2168110697207472</v>
+        <v>0.2170711920533397</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3221192583418636</v>
+        <v>0.317706665761838</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2025437733431583</v>
+        <v>0.2044437733431583</v>
       </c>
       <c r="C75">
-        <v>-224.0933359644225</v>
+        <v>-233.7829119458667</v>
       </c>
       <c r="D75">
-        <v>205.2312640355775</v>
+        <v>203.1118880541333</v>
       </c>
       <c r="E75">
-        <v>547.6046</v>
+        <v>555.1748</v>
       </c>
       <c r="F75">
-        <v>552.6246</v>
+        <v>560.1948</v>
       </c>
       <c r="G75">
         <v>123.3</v>
@@ -7437,37 +7437,37 @@
         <v>41.4</v>
       </c>
       <c r="M75">
-        <v>130.30888068</v>
+        <v>132.09393384</v>
       </c>
       <c r="N75">
-        <v>-88.90888068000001</v>
+        <v>-90.69393384</v>
       </c>
       <c r="O75">
-        <v>-22.22722017</v>
+        <v>-22.67348346</v>
       </c>
       <c r="P75">
-        <v>-66.68166051</v>
+        <v>-68.02045038</v>
       </c>
       <c r="Q75">
-        <v>-43.28166051</v>
+        <v>-44.62045038</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1632659375711866</v>
+        <v>0.1677838582470015</v>
       </c>
       <c r="T75">
-        <v>2.289629762497051</v>
+        <v>2.377692445670015</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07942666644045951</v>
+        <v>0.07835333311018304</v>
       </c>
       <c r="W75">
-        <v>0.2170711920533397</v>
+        <v>0.2173242840526189</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.317706665761838</v>
+        <v>0.3134133324407322</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2044437733431583</v>
+        <v>0.2063437733431583</v>
       </c>
       <c r="C76">
-        <v>-233.7829119458667</v>
+        <v>-243.4291627217525</v>
       </c>
       <c r="D76">
-        <v>203.1118880541333</v>
+        <v>201.0358372782475</v>
       </c>
       <c r="E76">
-        <v>555.1748</v>
+        <v>562.745</v>
       </c>
       <c r="F76">
-        <v>560.1948</v>
+        <v>567.765</v>
       </c>
       <c r="G76">
         <v>123.3</v>
@@ -7519,37 +7519,37 @@
         <v>41.4</v>
       </c>
       <c r="M76">
-        <v>132.09393384</v>
+        <v>133.878987</v>
       </c>
       <c r="N76">
-        <v>-90.69393384</v>
+        <v>-92.47898699999999</v>
       </c>
       <c r="O76">
-        <v>-22.67348346</v>
+        <v>-23.11974675</v>
       </c>
       <c r="P76">
-        <v>-68.02045038</v>
+        <v>-69.35924025</v>
       </c>
       <c r="Q76">
-        <v>-44.62045038</v>
+        <v>-45.95924025</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1677838582470015</v>
+        <v>0.1726632125768816</v>
       </c>
       <c r="T76">
-        <v>2.377692445670015</v>
+        <v>2.472800143496816</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07835333311018304</v>
+        <v>0.07730862200204727</v>
       </c>
       <c r="W76">
-        <v>0.2173242840526189</v>
+        <v>0.2175706269319173</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3134133324407322</v>
+        <v>0.3092344880081891</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2063437733431583</v>
+        <v>0.2082437733431584</v>
       </c>
       <c r="C77">
-        <v>-243.4291627217525</v>
+        <v>-253.0334033595313</v>
       </c>
       <c r="D77">
-        <v>201.0358372782475</v>
+        <v>199.0017966404687</v>
       </c>
       <c r="E77">
-        <v>562.745</v>
+        <v>570.3152</v>
       </c>
       <c r="F77">
-        <v>567.765</v>
+        <v>575.3352</v>
       </c>
       <c r="G77">
         <v>123.3</v>
@@ -7601,37 +7601,37 @@
         <v>41.4</v>
       </c>
       <c r="M77">
-        <v>133.878987</v>
+        <v>135.66404016</v>
       </c>
       <c r="N77">
-        <v>-92.47898699999999</v>
+        <v>-94.26404016000001</v>
       </c>
       <c r="O77">
-        <v>-23.11974675</v>
+        <v>-23.56601004</v>
       </c>
       <c r="P77">
-        <v>-69.35924025</v>
+        <v>-70.69803012</v>
       </c>
       <c r="Q77">
-        <v>-45.95924025</v>
+        <v>-47.29803012</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1726632125768816</v>
+        <v>0.177949179767585</v>
       </c>
       <c r="T77">
-        <v>2.472800143496816</v>
+        <v>2.575833482809183</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07730862200204727</v>
+        <v>0.076291403291494</v>
       </c>
       <c r="W77">
-        <v>0.2175706269319173</v>
+        <v>0.2178104871038657</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3092344880081891</v>
+        <v>0.305165613165976</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2082437733431584</v>
+        <v>0.2101437733431583</v>
       </c>
       <c r="C78">
-        <v>-253.0334033595313</v>
+        <v>-262.5968962373903</v>
       </c>
       <c r="D78">
-        <v>199.0017966404687</v>
+        <v>197.0085037626097</v>
       </c>
       <c r="E78">
-        <v>570.3152</v>
+        <v>577.8854</v>
       </c>
       <c r="F78">
-        <v>575.3352</v>
+        <v>582.9054</v>
       </c>
       <c r="G78">
         <v>123.3</v>
@@ -7683,37 +7683,37 @@
         <v>41.4</v>
       </c>
       <c r="M78">
-        <v>135.66404016</v>
+        <v>137.44909332</v>
       </c>
       <c r="N78">
-        <v>-94.26404016000001</v>
+        <v>-96.04909332</v>
       </c>
       <c r="O78">
-        <v>-23.56601004</v>
+        <v>-24.01227333</v>
       </c>
       <c r="P78">
-        <v>-70.69803012</v>
+        <v>-72.03681999</v>
       </c>
       <c r="Q78">
-        <v>-47.29803012</v>
+        <v>-48.63681999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.177949179767585</v>
+        <v>0.1836947962792191</v>
       </c>
       <c r="T78">
-        <v>2.575833482809183</v>
+        <v>2.687826242931322</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.076291403291494</v>
+        <v>0.07530060584614993</v>
       </c>
       <c r="W78">
-        <v>0.2178104871038657</v>
+        <v>0.2180441171414778</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.305165613165976</v>
+        <v>0.3012024233845998</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2101437733431583</v>
+        <v>0.2120437733431583</v>
       </c>
       <c r="C79">
-        <v>-262.5968962373903</v>
+        <v>-272.1208536568811</v>
       </c>
       <c r="D79">
-        <v>197.0085037626097</v>
+        <v>195.0547463431189</v>
       </c>
       <c r="E79">
-        <v>577.8854</v>
+        <v>585.4556</v>
       </c>
       <c r="F79">
-        <v>582.9054</v>
+        <v>590.4756</v>
       </c>
       <c r="G79">
         <v>123.3</v>
@@ -7765,37 +7765,37 @@
         <v>41.4</v>
       </c>
       <c r="M79">
-        <v>137.44909332</v>
+        <v>139.23414648</v>
       </c>
       <c r="N79">
-        <v>-96.04909332</v>
+        <v>-97.83414647999999</v>
       </c>
       <c r="O79">
-        <v>-24.01227333</v>
+        <v>-24.45853662</v>
       </c>
       <c r="P79">
-        <v>-72.03681999</v>
+        <v>-73.37560986</v>
       </c>
       <c r="Q79">
-        <v>-48.63681999</v>
+        <v>-49.97560986</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1836947962792191</v>
+        <v>0.1899627415646381</v>
       </c>
       <c r="T79">
-        <v>2.687826242931322</v>
+        <v>2.810000163064563</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07530060584614993</v>
+        <v>0.07433521346350699</v>
       </c>
       <c r="W79">
-        <v>0.2180441171414778</v>
+        <v>0.218271756665305</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3012024233845998</v>
+        <v>0.297340853854028</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2120437733431583</v>
+        <v>0.2139437733431583</v>
       </c>
       <c r="C80">
-        <v>-272.1208536568811</v>
+        <v>-281.6064403016177</v>
       </c>
       <c r="D80">
-        <v>195.0547463431189</v>
+        <v>193.1393596983823</v>
       </c>
       <c r="E80">
-        <v>585.4556</v>
+        <v>593.0258</v>
       </c>
       <c r="F80">
-        <v>590.4756</v>
+        <v>598.0458</v>
       </c>
       <c r="G80">
         <v>123.3</v>
@@ -7847,37 +7847,37 @@
         <v>41.4</v>
       </c>
       <c r="M80">
-        <v>139.23414648</v>
+        <v>141.01919964</v>
       </c>
       <c r="N80">
-        <v>-97.83414647999999</v>
+        <v>-99.61919964000001</v>
       </c>
       <c r="O80">
-        <v>-24.45853662</v>
+        <v>-24.90479991</v>
       </c>
       <c r="P80">
-        <v>-73.37560986</v>
+        <v>-74.71439973</v>
       </c>
       <c r="Q80">
-        <v>-49.97560986</v>
+        <v>-51.31439973</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1899627415646381</v>
+        <v>0.1968276340200971</v>
       </c>
       <c r="T80">
-        <v>2.810000163064563</v>
+        <v>2.943809694639067</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07433521346350699</v>
+        <v>0.07339426139434867</v>
       </c>
       <c r="W80">
-        <v>0.218271756665305</v>
+        <v>0.2184936331632126</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.297340853854028</v>
+        <v>0.2935770455773947</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2139437733431583</v>
+        <v>0.2158437733431584</v>
       </c>
       <c r="C81">
-        <v>-281.6064403016177</v>
+        <v>-291.0547755525192</v>
       </c>
       <c r="D81">
-        <v>193.1393596983823</v>
+        <v>191.2612244474807</v>
       </c>
       <c r="E81">
-        <v>593.0258</v>
+        <v>600.596</v>
       </c>
       <c r="F81">
-        <v>598.0458</v>
+        <v>605.616</v>
       </c>
       <c r="G81">
         <v>123.3</v>
@@ -7929,37 +7929,37 @@
         <v>41.4</v>
       </c>
       <c r="M81">
-        <v>141.01919964</v>
+        <v>142.8042528</v>
       </c>
       <c r="N81">
-        <v>-99.61919964000001</v>
+        <v>-101.4042528</v>
       </c>
       <c r="O81">
-        <v>-24.90479991</v>
+        <v>-25.3510632</v>
       </c>
       <c r="P81">
-        <v>-74.71439973</v>
+        <v>-76.0531896</v>
       </c>
       <c r="Q81">
-        <v>-51.31439973</v>
+        <v>-52.6531896</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1968276340200971</v>
+        <v>0.204379015721102</v>
       </c>
       <c r="T81">
-        <v>2.943809694639067</v>
+        <v>3.09100017937102</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07339426139434867</v>
+        <v>0.07247683312691931</v>
       </c>
       <c r="W81">
-        <v>0.2184936331632126</v>
+        <v>0.2187099627486724</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2935770455773947</v>
+        <v>0.2899073325076773</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2158437733431584</v>
+        <v>0.2177437733431583</v>
       </c>
       <c r="C82">
-        <v>-291.0547755525192</v>
+        <v>-300.466935669271</v>
       </c>
       <c r="D82">
-        <v>191.2612244474807</v>
+        <v>189.419264330729</v>
       </c>
       <c r="E82">
-        <v>600.596</v>
+        <v>608.1662</v>
       </c>
       <c r="F82">
-        <v>605.616</v>
+        <v>613.1862</v>
       </c>
       <c r="G82">
         <v>123.3</v>
@@ -8011,37 +8011,37 @@
         <v>41.4</v>
       </c>
       <c r="M82">
-        <v>142.8042528</v>
+        <v>144.58930596</v>
       </c>
       <c r="N82">
-        <v>-101.4042528</v>
+        <v>-103.18930596</v>
       </c>
       <c r="O82">
-        <v>-25.3510632</v>
+        <v>-25.79732649</v>
       </c>
       <c r="P82">
-        <v>-76.0531896</v>
+        <v>-77.39197947</v>
       </c>
       <c r="Q82">
-        <v>-52.6531896</v>
+        <v>-53.99197947</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.204379015721102</v>
+        <v>0.2127252797064231</v>
       </c>
       <c r="T82">
-        <v>3.09100017937102</v>
+        <v>3.253684399337916</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07247683312691931</v>
+        <v>0.07158205740930303</v>
       </c>
       <c r="W82">
-        <v>0.2187099627486724</v>
+        <v>0.2189209508628863</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2899073325076773</v>
+        <v>0.2863282296372122</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2177437733431583</v>
+        <v>0.2196437733431583</v>
       </c>
       <c r="C83">
-        <v>-300.466935669271</v>
+        <v>-309.8439558469339</v>
       </c>
       <c r="D83">
-        <v>189.419264330729</v>
+        <v>187.6124441530661</v>
       </c>
       <c r="E83">
-        <v>608.1662</v>
+        <v>615.7364</v>
       </c>
       <c r="F83">
-        <v>613.1862</v>
+        <v>620.7564</v>
       </c>
       <c r="G83">
         <v>123.3</v>
@@ -8093,37 +8093,37 @@
         <v>41.4</v>
       </c>
       <c r="M83">
-        <v>144.58930596</v>
+        <v>146.37435912</v>
       </c>
       <c r="N83">
-        <v>-103.18930596</v>
+        <v>-104.97435912</v>
       </c>
       <c r="O83">
-        <v>-25.79732649</v>
+        <v>-26.24358978</v>
       </c>
       <c r="P83">
-        <v>-77.39197947</v>
+        <v>-78.73076933999999</v>
       </c>
       <c r="Q83">
-        <v>-53.99197947</v>
+        <v>-55.33076934</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2127252797064231</v>
+        <v>0.22199890635678</v>
       </c>
       <c r="T83">
-        <v>3.253684399337916</v>
+        <v>3.434444643745579</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07158205740930303</v>
+        <v>0.07070910548967738</v>
       </c>
       <c r="W83">
-        <v>0.2189209508628863</v>
+        <v>0.2191267929255341</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2863282296372122</v>
+        <v>0.2828364219587095</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2196437733431583</v>
+        <v>0.2215437733431584</v>
       </c>
       <c r="C84">
-        <v>-309.8439558469339</v>
+        <v>-319.1868321559632</v>
       </c>
       <c r="D84">
-        <v>187.6124441530661</v>
+        <v>185.8397678440368</v>
       </c>
       <c r="E84">
-        <v>615.7364</v>
+        <v>623.3066</v>
       </c>
       <c r="F84">
-        <v>620.7564</v>
+        <v>628.3266</v>
       </c>
       <c r="G84">
         <v>123.3</v>
@@ -8175,37 +8175,37 @@
         <v>41.4</v>
       </c>
       <c r="M84">
-        <v>146.37435912</v>
+        <v>148.15941228</v>
       </c>
       <c r="N84">
-        <v>-104.97435912</v>
+        <v>-106.75941228</v>
       </c>
       <c r="O84">
-        <v>-26.24358978</v>
+        <v>-26.68985307</v>
       </c>
       <c r="P84">
-        <v>-78.73076933999999</v>
+        <v>-80.06955920999999</v>
       </c>
       <c r="Q84">
-        <v>-55.33076934</v>
+        <v>-56.66955921</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.22199890635678</v>
+        <v>0.2323635479071788</v>
       </c>
       <c r="T84">
-        <v>3.434444643745579</v>
+        <v>3.636470799260024</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07070910548967738</v>
+        <v>0.0698571885560668</v>
       </c>
       <c r="W84">
-        <v>0.2191267929255341</v>
+        <v>0.2193276749384795</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2828364219587095</v>
+        <v>0.2794287542242673</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2215437733431584</v>
+        <v>0.2234437733431584</v>
       </c>
       <c r="C85">
-        <v>-319.1868321559632</v>
+        <v>-328.4965233732712</v>
       </c>
       <c r="D85">
-        <v>185.8397678440368</v>
+        <v>184.1002766267289</v>
       </c>
       <c r="E85">
-        <v>623.3066</v>
+        <v>630.8768000000001</v>
       </c>
       <c r="F85">
-        <v>628.3266</v>
+        <v>635.8968000000001</v>
       </c>
       <c r="G85">
         <v>123.3</v>
@@ -8257,37 +8257,37 @@
         <v>41.4</v>
       </c>
       <c r="M85">
-        <v>148.15941228</v>
+        <v>149.94446544</v>
       </c>
       <c r="N85">
-        <v>-106.75941228</v>
+        <v>-108.54446544</v>
       </c>
       <c r="O85">
-        <v>-26.68985307</v>
+        <v>-27.13611636</v>
       </c>
       <c r="P85">
-        <v>-80.06955920999999</v>
+        <v>-81.40834908000001</v>
       </c>
       <c r="Q85">
-        <v>-56.66955921</v>
+        <v>-58.00834908000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2323635479071788</v>
+        <v>0.2440237696513775</v>
       </c>
       <c r="T85">
-        <v>3.636470799260024</v>
+        <v>3.863750224213777</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0698571885560668</v>
+        <v>0.06902555535897076</v>
       </c>
       <c r="W85">
-        <v>0.2193276749384795</v>
+        <v>0.2195237740463547</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2794287542242673</v>
+        <v>0.2761022214358831</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2234437733431583</v>
+        <v>0.2253437733431583</v>
       </c>
       <c r="C86">
-        <v>-328.496523373271</v>
+        <v>-337.7739527114114</v>
       </c>
       <c r="D86">
-        <v>184.100276626729</v>
+        <v>182.3930472885886</v>
       </c>
       <c r="E86">
-        <v>630.8768</v>
+        <v>638.447</v>
       </c>
       <c r="F86">
-        <v>635.8968</v>
+        <v>643.467</v>
       </c>
       <c r="G86">
         <v>123.3</v>
@@ -8339,37 +8339,37 @@
         <v>41.4</v>
       </c>
       <c r="M86">
-        <v>149.94446544</v>
+        <v>151.7295186</v>
       </c>
       <c r="N86">
-        <v>-108.54446544</v>
+        <v>-110.3295186</v>
       </c>
       <c r="O86">
-        <v>-27.13611636</v>
+        <v>-27.58237965</v>
       </c>
       <c r="P86">
-        <v>-81.40834908000001</v>
+        <v>-82.74713894999999</v>
       </c>
       <c r="Q86">
-        <v>-58.00834908000001</v>
+        <v>-59.34713894999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2440237696513774</v>
+        <v>0.2572386876281359</v>
       </c>
       <c r="T86">
-        <v>3.863750224213774</v>
+        <v>4.121333572494692</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06902555535897076</v>
+        <v>0.0682134900018064</v>
       </c>
       <c r="W86">
-        <v>0.2195237740463547</v>
+        <v>0.2197152590575741</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2761022214358831</v>
+        <v>0.2728539600072257</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2253437733431583</v>
+        <v>0.2272437733431584</v>
       </c>
       <c r="C87">
-        <v>-337.7739527114114</v>
+        <v>-347.0200094524344</v>
       </c>
       <c r="D87">
-        <v>182.3930472885886</v>
+        <v>180.7171905475657</v>
       </c>
       <c r="E87">
-        <v>638.447</v>
+        <v>646.0172</v>
       </c>
       <c r="F87">
-        <v>643.467</v>
+        <v>651.0372</v>
       </c>
       <c r="G87">
         <v>123.3</v>
@@ -8421,37 +8421,37 @@
         <v>41.4</v>
       </c>
       <c r="M87">
-        <v>151.7295186</v>
+        <v>153.51457176</v>
       </c>
       <c r="N87">
-        <v>-110.3295186</v>
+        <v>-112.11457176</v>
       </c>
       <c r="O87">
-        <v>-27.58237965</v>
+        <v>-28.02864294</v>
       </c>
       <c r="P87">
-        <v>-82.74713894999999</v>
+        <v>-84.08592881999999</v>
       </c>
       <c r="Q87">
-        <v>-59.34713894999999</v>
+        <v>-60.68592881999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2572386876281359</v>
+        <v>0.2723414510301456</v>
       </c>
       <c r="T87">
-        <v>4.121333572494692</v>
+        <v>4.415714541958599</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0682134900018064</v>
+        <v>0.06742030988550633</v>
       </c>
       <c r="W87">
-        <v>0.2197152590575741</v>
+        <v>0.2199022909289976</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2728539600072257</v>
+        <v>0.2696812395420254</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2272437733431584</v>
+        <v>0.2291437733431584</v>
       </c>
       <c r="C88">
-        <v>-347.0200094524344</v>
+        <v>-356.2355504924894</v>
       </c>
       <c r="D88">
-        <v>180.7171905475657</v>
+        <v>179.0718495075106</v>
       </c>
       <c r="E88">
-        <v>646.0172</v>
+        <v>653.5874</v>
       </c>
       <c r="F88">
-        <v>651.0372</v>
+        <v>658.6074</v>
       </c>
       <c r="G88">
         <v>123.3</v>
@@ -8503,37 +8503,37 @@
         <v>41.4</v>
       </c>
       <c r="M88">
-        <v>153.51457176</v>
+        <v>155.29962492</v>
       </c>
       <c r="N88">
-        <v>-112.11457176</v>
+        <v>-113.89962492</v>
       </c>
       <c r="O88">
-        <v>-28.02864294</v>
+        <v>-28.47490623</v>
       </c>
       <c r="P88">
-        <v>-84.08592881999999</v>
+        <v>-85.42471869000001</v>
       </c>
       <c r="Q88">
-        <v>-60.68592881999999</v>
+        <v>-62.02471869000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2723414510301456</v>
+        <v>0.289767716494003</v>
       </c>
       <c r="T88">
-        <v>4.415714541958599</v>
+        <v>4.75538489134003</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06742030988550633</v>
+        <v>0.06664536379486832</v>
       </c>
       <c r="W88">
-        <v>0.2199022909289976</v>
+        <v>0.2200850232171701</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2696812395420254</v>
+        <v>0.2665814551794733</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2291437733431584</v>
+        <v>0.2310437733431583</v>
       </c>
       <c r="C89">
-        <v>-356.2355504924894</v>
+        <v>-365.4214018028118</v>
       </c>
       <c r="D89">
-        <v>179.0718495075106</v>
+        <v>177.4561981971882</v>
       </c>
       <c r="E89">
-        <v>653.5874</v>
+        <v>661.1576</v>
       </c>
       <c r="F89">
-        <v>658.6074</v>
+        <v>666.1776</v>
       </c>
       <c r="G89">
         <v>123.3</v>
@@ -8585,37 +8585,37 @@
         <v>41.4</v>
       </c>
       <c r="M89">
-        <v>155.29962492</v>
+        <v>157.08467808</v>
       </c>
       <c r="N89">
-        <v>-113.89962492</v>
+        <v>-115.68467808</v>
       </c>
       <c r="O89">
-        <v>-28.47490623</v>
+        <v>-28.92116952</v>
       </c>
       <c r="P89">
-        <v>-85.42471869000001</v>
+        <v>-86.76350855999999</v>
       </c>
       <c r="Q89">
-        <v>-62.02471869000001</v>
+        <v>-63.36350855999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.289767716494003</v>
+        <v>0.3100983595351698</v>
       </c>
       <c r="T89">
-        <v>4.75538489134003</v>
+        <v>5.151666965618365</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06664536379486832</v>
+        <v>0.06588803011538119</v>
       </c>
       <c r="W89">
-        <v>0.2200850232171701</v>
+        <v>0.2202636024987931</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2665814551794733</v>
+        <v>0.2635521204615248</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2310437733431583</v>
+        <v>0.2329437733431584</v>
       </c>
       <c r="C90">
-        <v>-365.4214018028118</v>
+        <v>-374.5783598123278</v>
       </c>
       <c r="D90">
-        <v>177.4561981971882</v>
+        <v>175.8694401876722</v>
       </c>
       <c r="E90">
-        <v>661.1576</v>
+        <v>668.7278</v>
       </c>
       <c r="F90">
-        <v>666.1776</v>
+        <v>673.7478</v>
       </c>
       <c r="G90">
         <v>123.3</v>
@@ -8667,37 +8667,37 @@
         <v>41.4</v>
       </c>
       <c r="M90">
-        <v>157.08467808</v>
+        <v>158.86973124</v>
       </c>
       <c r="N90">
-        <v>-115.68467808</v>
+        <v>-117.46973124</v>
       </c>
       <c r="O90">
-        <v>-28.92116952</v>
+        <v>-29.36743281</v>
       </c>
       <c r="P90">
-        <v>-86.76350855999999</v>
+        <v>-88.10229842999999</v>
       </c>
       <c r="Q90">
-        <v>-63.36350855999999</v>
+        <v>-64.70229842999998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3100983595351698</v>
+        <v>0.3341254831292763</v>
       </c>
       <c r="T90">
-        <v>5.151666965618365</v>
+        <v>5.620000326129126</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06588803011538119</v>
+        <v>0.06514771517026455</v>
       </c>
       <c r="W90">
-        <v>0.2202636024987931</v>
+        <v>0.2204381687628516</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2635521204615248</v>
+        <v>0.2605908606810583</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2329437733431584</v>
+        <v>0.2348437733431583</v>
       </c>
       <c r="C91">
-        <v>-374.5783598123278</v>
+        <v>-383.7071927167394</v>
       </c>
       <c r="D91">
-        <v>175.8694401876722</v>
+        <v>174.3108072832606</v>
       </c>
       <c r="E91">
-        <v>668.7278</v>
+        <v>676.298</v>
       </c>
       <c r="F91">
-        <v>673.7478</v>
+        <v>681.318</v>
       </c>
       <c r="G91">
         <v>123.3</v>
@@ -8749,37 +8749,37 @@
         <v>41.4</v>
       </c>
       <c r="M91">
-        <v>158.86973124</v>
+        <v>160.6547844</v>
       </c>
       <c r="N91">
-        <v>-117.46973124</v>
+        <v>-119.2547844</v>
       </c>
       <c r="O91">
-        <v>-29.36743281</v>
+        <v>-29.8136961</v>
       </c>
       <c r="P91">
-        <v>-88.10229842999999</v>
+        <v>-89.4410883</v>
       </c>
       <c r="Q91">
-        <v>-64.70229842999998</v>
+        <v>-66.04108830000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3341254831292763</v>
+        <v>0.3629580314422038</v>
       </c>
       <c r="T91">
-        <v>5.620000326129126</v>
+        <v>6.182000358742039</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06514771517026455</v>
+        <v>0.06442385166837272</v>
       </c>
       <c r="W91">
-        <v>0.2204381687628516</v>
+        <v>0.2206088557765977</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2605908606810583</v>
+        <v>0.2576954066734909</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2348437733431583</v>
+        <v>0.2367437733431583</v>
       </c>
       <c r="C92">
-        <v>-383.7071927167394</v>
+        <v>-392.8086417186108</v>
       </c>
       <c r="D92">
-        <v>174.3108072832606</v>
+        <v>172.7795582813892</v>
       </c>
       <c r="E92">
-        <v>676.298</v>
+        <v>683.8682</v>
       </c>
       <c r="F92">
-        <v>681.318</v>
+        <v>688.8882</v>
       </c>
       <c r="G92">
         <v>123.3</v>
@@ -8831,37 +8831,37 @@
         <v>41.4</v>
       </c>
       <c r="M92">
-        <v>160.6547844</v>
+        <v>162.43983756</v>
       </c>
       <c r="N92">
-        <v>-119.2547844</v>
+        <v>-121.03983756</v>
       </c>
       <c r="O92">
-        <v>-29.8136961</v>
+        <v>-30.25995939</v>
       </c>
       <c r="P92">
-        <v>-89.4410883</v>
+        <v>-90.77987816999999</v>
       </c>
       <c r="Q92">
-        <v>-66.04108830000001</v>
+        <v>-67.37987816999998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3629580314422038</v>
+        <v>0.3981978127135599</v>
       </c>
       <c r="T92">
-        <v>6.182000358742039</v>
+        <v>6.868889287491156</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06442385166837272</v>
+        <v>0.06371589725443456</v>
       </c>
       <c r="W92">
-        <v>0.2206088557765977</v>
+        <v>0.2207757914274043</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2576954066734909</v>
+        <v>0.2548635890177383</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2367437733431583</v>
+        <v>0.2386437733431583</v>
       </c>
       <c r="C93">
-        <v>-392.8086417186108</v>
+        <v>-401.8834222026628</v>
       </c>
       <c r="D93">
-        <v>172.7795582813892</v>
+        <v>171.2749777973372</v>
       </c>
       <c r="E93">
-        <v>683.8682</v>
+        <v>691.4384</v>
       </c>
       <c r="F93">
-        <v>688.8882</v>
+        <v>696.4584</v>
       </c>
       <c r="G93">
         <v>123.3</v>
@@ -8913,37 +8913,37 @@
         <v>41.4</v>
       </c>
       <c r="M93">
-        <v>162.43983756</v>
+        <v>164.22489072</v>
       </c>
       <c r="N93">
-        <v>-121.03983756</v>
+        <v>-122.82489072</v>
       </c>
       <c r="O93">
-        <v>-30.25995939</v>
+        <v>-30.70622268</v>
       </c>
       <c r="P93">
-        <v>-90.77987816999999</v>
+        <v>-92.11866803999999</v>
       </c>
       <c r="Q93">
-        <v>-67.37987816999998</v>
+        <v>-68.71866803999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3981978127135599</v>
+        <v>0.442247539302755</v>
       </c>
       <c r="T93">
-        <v>6.868889287491156</v>
+        <v>7.727500448427553</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06371589725443456</v>
+        <v>0.06302333315384288</v>
       </c>
       <c r="W93">
-        <v>0.2207757914274043</v>
+        <v>0.2209390980423239</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2548635890177383</v>
+        <v>0.2520933326153716</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2386437733431583</v>
+        <v>0.2405437733431583</v>
       </c>
       <c r="C94">
-        <v>-401.8834222026628</v>
+        <v>-410.9322248501884</v>
       </c>
       <c r="D94">
-        <v>171.2749777973372</v>
+        <v>169.7963751498116</v>
       </c>
       <c r="E94">
-        <v>691.4384</v>
+        <v>699.0086</v>
       </c>
       <c r="F94">
-        <v>696.4584</v>
+        <v>704.0286</v>
       </c>
       <c r="G94">
         <v>123.3</v>
@@ -8995,37 +8995,37 @@
         <v>41.4</v>
       </c>
       <c r="M94">
-        <v>164.22489072</v>
+        <v>166.00994388</v>
       </c>
       <c r="N94">
-        <v>-122.82489072</v>
+        <v>-124.60994388</v>
       </c>
       <c r="O94">
-        <v>-30.70622268</v>
+        <v>-31.15248597</v>
       </c>
       <c r="P94">
-        <v>-92.11866803999999</v>
+        <v>-93.45745791</v>
       </c>
       <c r="Q94">
-        <v>-68.71866803999998</v>
+        <v>-70.05745791000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.442247539302755</v>
+        <v>0.4988829020602915</v>
       </c>
       <c r="T94">
-        <v>7.727500448427553</v>
+        <v>8.831429083917204</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06302333315384288</v>
+        <v>0.06234566290487682</v>
       </c>
       <c r="W94">
-        <v>0.2209390980423239</v>
+        <v>0.22109889268703</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2520933326153716</v>
+        <v>0.2493826516195073</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2405437733431583</v>
+        <v>0.2424437733431583</v>
       </c>
       <c r="C95">
-        <v>-410.9322248501884</v>
+        <v>-419.9557166962401</v>
       </c>
       <c r="D95">
-        <v>169.7963751498116</v>
+        <v>168.3430833037599</v>
       </c>
       <c r="E95">
-        <v>699.0086</v>
+        <v>706.5788</v>
       </c>
       <c r="F95">
-        <v>704.0286</v>
+        <v>711.5988</v>
       </c>
       <c r="G95">
         <v>123.3</v>
@@ -9077,37 +9077,37 @@
         <v>41.4</v>
       </c>
       <c r="M95">
-        <v>166.00994388</v>
+        <v>167.79499704</v>
       </c>
       <c r="N95">
-        <v>-124.60994388</v>
+        <v>-126.39499704</v>
       </c>
       <c r="O95">
-        <v>-31.15248597</v>
+        <v>-31.59874926</v>
       </c>
       <c r="P95">
-        <v>-93.45745791</v>
+        <v>-94.79624777999999</v>
       </c>
       <c r="Q95">
-        <v>-70.05745791000001</v>
+        <v>-71.39624777999998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4988829020602915</v>
+        <v>0.5743967190703402</v>
       </c>
       <c r="T95">
-        <v>8.831429083917204</v>
+        <v>10.30333393123674</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06234566290487682</v>
+        <v>0.06168241117184622</v>
       </c>
       <c r="W95">
-        <v>0.22109889268703</v>
+        <v>0.2212552874456787</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2493826516195073</v>
+        <v>0.2467296446873849</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2424437733431583</v>
+        <v>0.2443437733431584</v>
       </c>
       <c r="C96">
-        <v>-419.9557166962401</v>
+        <v>-428.9545421329861</v>
       </c>
       <c r="D96">
-        <v>168.3430833037599</v>
+        <v>166.9144578670139</v>
       </c>
       <c r="E96">
-        <v>706.5788</v>
+        <v>714.149</v>
       </c>
       <c r="F96">
-        <v>711.5988</v>
+        <v>719.169</v>
       </c>
       <c r="G96">
         <v>123.3</v>
@@ -9159,37 +9159,37 @@
         <v>41.4</v>
       </c>
       <c r="M96">
-        <v>167.79499704</v>
+        <v>169.5800502</v>
       </c>
       <c r="N96">
-        <v>-126.39499704</v>
+        <v>-128.1800502</v>
       </c>
       <c r="O96">
-        <v>-31.59874926</v>
+        <v>-32.04501255</v>
       </c>
       <c r="P96">
-        <v>-94.79624777999999</v>
+        <v>-96.13503765000002</v>
       </c>
       <c r="Q96">
-        <v>-71.39624777999998</v>
+        <v>-72.73503765000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5743967190703402</v>
+        <v>0.6801160628844086</v>
       </c>
       <c r="T96">
-        <v>10.30333393123674</v>
+        <v>12.3640007174841</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06168241117184622</v>
+        <v>0.0610331226331952</v>
       </c>
       <c r="W96">
-        <v>0.2212552874456787</v>
+        <v>0.2214083896830926</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2467296446873849</v>
+        <v>0.2441324905327809</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2443437733431584</v>
+        <v>0.2462437733431583</v>
       </c>
       <c r="C97">
-        <v>-428.9545421329861</v>
+        <v>-437.929323862407</v>
       </c>
       <c r="D97">
-        <v>166.9144578670139</v>
+        <v>165.5098761375931</v>
       </c>
       <c r="E97">
-        <v>714.149</v>
+        <v>721.7192000000001</v>
       </c>
       <c r="F97">
-        <v>719.169</v>
+        <v>726.7392000000001</v>
       </c>
       <c r="G97">
         <v>123.3</v>
@@ -9241,37 +9241,37 @@
         <v>41.4</v>
       </c>
       <c r="M97">
-        <v>169.5800502</v>
+        <v>171.36510336</v>
       </c>
       <c r="N97">
-        <v>-128.1800502</v>
+        <v>-129.96510336</v>
       </c>
       <c r="O97">
-        <v>-32.04501255</v>
+        <v>-32.49127584000001</v>
       </c>
       <c r="P97">
-        <v>-96.13503765000002</v>
+        <v>-97.47382752000001</v>
       </c>
       <c r="Q97">
-        <v>-72.73503765000001</v>
+        <v>-74.07382752000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6801160628844086</v>
+        <v>0.8386950786055111</v>
       </c>
       <c r="T97">
-        <v>12.3640007174841</v>
+        <v>15.45500089685513</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0610331226331952</v>
+        <v>0.06039736093909941</v>
       </c>
       <c r="W97">
-        <v>0.2214083896830926</v>
+        <v>0.2215583022905604</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2441324905327809</v>
+        <v>0.2415894437563977</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2462437733431583</v>
+        <v>0.2481437733431583</v>
       </c>
       <c r="C98">
-        <v>-437.9293238624069</v>
+        <v>-446.880663801293</v>
       </c>
       <c r="D98">
-        <v>165.5098761375931</v>
+        <v>164.128736198707</v>
       </c>
       <c r="E98">
-        <v>721.7192</v>
+        <v>729.2894</v>
       </c>
       <c r="F98">
-        <v>726.7392</v>
+        <v>734.3094</v>
       </c>
       <c r="G98">
         <v>123.3</v>
@@ -9323,37 +9323,37 @@
         <v>41.4</v>
       </c>
       <c r="M98">
-        <v>171.36510336</v>
+        <v>173.15015652</v>
       </c>
       <c r="N98">
-        <v>-129.96510336</v>
+        <v>-131.75015652</v>
       </c>
       <c r="O98">
-        <v>-32.49127584</v>
+        <v>-32.93753913</v>
       </c>
       <c r="P98">
-        <v>-97.47382752</v>
+        <v>-98.81261738999999</v>
       </c>
       <c r="Q98">
-        <v>-74.07382752000001</v>
+        <v>-75.41261738999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.838695078605509</v>
+        <v>1.102993438140679</v>
       </c>
       <c r="T98">
-        <v>15.45500089685508</v>
+        <v>20.60666786247345</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06039736093909942</v>
+        <v>0.0597747077335417</v>
       </c>
       <c r="W98">
-        <v>0.2215583022905604</v>
+        <v>0.2217051239164309</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2415894437563977</v>
+        <v>0.2390988309341668</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2481437733431583</v>
+        <v>0.2500437733431584</v>
       </c>
       <c r="C99">
-        <v>-446.880663801293</v>
+        <v>-455.8091439413039</v>
       </c>
       <c r="D99">
-        <v>164.128736198707</v>
+        <v>162.7704560586961</v>
       </c>
       <c r="E99">
-        <v>729.2894</v>
+        <v>736.8596</v>
       </c>
       <c r="F99">
-        <v>734.3094</v>
+        <v>741.8796</v>
       </c>
       <c r="G99">
         <v>123.3</v>
@@ -9405,37 +9405,37 @@
         <v>41.4</v>
       </c>
       <c r="M99">
-        <v>173.15015652</v>
+        <v>174.93520968</v>
       </c>
       <c r="N99">
-        <v>-131.75015652</v>
+        <v>-133.53520968</v>
       </c>
       <c r="O99">
-        <v>-32.93753913</v>
+        <v>-33.38380242</v>
       </c>
       <c r="P99">
-        <v>-98.81261738999999</v>
+        <v>-100.15140726</v>
       </c>
       <c r="Q99">
-        <v>-75.41261738999998</v>
+        <v>-76.75140726000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.102993438140679</v>
+        <v>1.631590157211018</v>
       </c>
       <c r="T99">
-        <v>20.60666786247345</v>
+        <v>30.91000179371017</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0597747077335417</v>
+        <v>0.05916476173626066</v>
       </c>
       <c r="W99">
-        <v>0.2217051239164309</v>
+        <v>0.2218489491825898</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2390988309341668</v>
+        <v>0.2366590469450427</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2500437733431584</v>
+        <v>0.2519437733431583</v>
       </c>
       <c r="C100">
-        <v>-455.8091439413039</v>
+        <v>-464.7153271666738</v>
       </c>
       <c r="D100">
-        <v>162.7704560586961</v>
+        <v>161.4344728333262</v>
       </c>
       <c r="E100">
-        <v>736.8596</v>
+        <v>744.4298</v>
       </c>
       <c r="F100">
-        <v>741.8796</v>
+        <v>749.4498</v>
       </c>
       <c r="G100">
         <v>123.3</v>
@@ -9487,37 +9487,37 @@
         <v>41.4</v>
       </c>
       <c r="M100">
-        <v>174.93520968</v>
+        <v>176.72026284</v>
       </c>
       <c r="N100">
-        <v>-133.53520968</v>
+        <v>-135.32026284</v>
       </c>
       <c r="O100">
-        <v>-33.38380242</v>
+        <v>-33.83006571</v>
       </c>
       <c r="P100">
-        <v>-100.15140726</v>
+        <v>-101.49019713</v>
       </c>
       <c r="Q100">
-        <v>-76.75140726000001</v>
+        <v>-78.09019713000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.631590157211018</v>
+        <v>3.217380314422036</v>
       </c>
       <c r="T100">
-        <v>30.91000179371017</v>
+        <v>61.82000358742034</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05916476173626066</v>
+        <v>0.05856713788033883</v>
       </c>
       <c r="W100">
-        <v>0.2218489491825898</v>
+        <v>0.2219898688878161</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2366590469450427</v>
+        <v>0.2342685515213554</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2519437733431583</v>
-      </c>
-      <c r="C101">
-        <v>-464.7153271666738</v>
-      </c>
-      <c r="D101">
-        <v>161.4344728333262</v>
-      </c>
-      <c r="E101">
-        <v>744.4298</v>
-      </c>
-      <c r="F101">
-        <v>749.4498</v>
-      </c>
-      <c r="G101">
-        <v>123.3</v>
-      </c>
-      <c r="H101">
-        <v>752</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>64.8</v>
-      </c>
-      <c r="K101">
-        <v>23.4</v>
-      </c>
-      <c r="L101">
-        <v>41.4</v>
-      </c>
-      <c r="M101">
-        <v>176.72026284</v>
-      </c>
-      <c r="N101">
-        <v>-135.32026284</v>
-      </c>
-      <c r="O101">
-        <v>-33.83006571</v>
-      </c>
-      <c r="P101">
-        <v>-101.49019713</v>
-      </c>
-      <c r="Q101">
-        <v>-78.09019713000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.217380314422036</v>
-      </c>
-      <c r="T101">
-        <v>61.82000358742034</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05856713788033883</v>
-      </c>
-      <c r="W101">
-        <v>0.2219898688878161</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2342685515213554</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
